--- a/research/traditional_assets/database/data/mexico/mexico_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_transportation_railroads.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0797176745613359</v>
+        <v>0.07951002153765187</v>
       </c>
       <c r="C2">
-        <v>8601.265967307307</v>
+        <v>8542.699382469722</v>
       </c>
       <c r="D2">
-        <v>8276.365967307307</v>
+        <v>8305.950382469722</v>
       </c>
       <c r="E2">
-        <v>-1986.7</v>
+        <v>-1898.549</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>88.15100000000001</v>
       </c>
       <c r="G2">
         <v>324.9</v>
@@ -1457,28 +1457,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.4339953</v>
       </c>
       <c r="N2">
-        <v>783.6999999999999</v>
+        <v>779.2660046999999</v>
       </c>
       <c r="O2">
-        <v>235.11</v>
+        <v>233.77980141</v>
       </c>
       <c r="P2">
-        <v>548.5899999999999</v>
+        <v>545.4862032899999</v>
       </c>
       <c r="Q2">
-        <v>942.9899999999999</v>
+        <v>939.8862032899999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0797176745613359</v>
+        <v>0.07995749650267867</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969562</v>
+        <v>0.4970331937576417</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>176.7480448163759</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07951002153765187</v>
+        <v>0.07930236851396789</v>
       </c>
       <c r="C3">
-        <v>8542.699382469722</v>
+        <v>8484.345059255642</v>
       </c>
       <c r="D3">
-        <v>8305.950382469722</v>
+        <v>8335.747059255642</v>
       </c>
       <c r="E3">
-        <v>-1898.549</v>
+        <v>-1810.398</v>
       </c>
       <c r="F3">
-        <v>88.15100000000001</v>
+        <v>176.302</v>
       </c>
       <c r="G3">
         <v>324.9</v>
@@ -1539,28 +1539,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M3">
-        <v>4.4339953</v>
+        <v>8.867990600000001</v>
       </c>
       <c r="N3">
-        <v>779.2660046999999</v>
+        <v>774.8320093999999</v>
       </c>
       <c r="O3">
-        <v>233.77980141</v>
+        <v>232.44960282</v>
       </c>
       <c r="P3">
-        <v>545.4862032899999</v>
+        <v>542.38240658</v>
       </c>
       <c r="Q3">
-        <v>939.8862032899999</v>
+        <v>936.7824065799999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07995749650267867</v>
+        <v>0.08020221276935499</v>
       </c>
       <c r="T3">
-        <v>0.4970331937576417</v>
+        <v>0.5005941136154841</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>176.7480448163759</v>
+        <v>88.37402240818793</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07930236851396789</v>
+        <v>0.07909471549028387</v>
       </c>
       <c r="C4">
-        <v>8484.345059255642</v>
+        <v>8426.205290284774</v>
       </c>
       <c r="D4">
-        <v>8335.747059255642</v>
+        <v>8365.758290284773</v>
       </c>
       <c r="E4">
-        <v>-1810.398</v>
+        <v>-1722.247</v>
       </c>
       <c r="F4">
-        <v>176.302</v>
+        <v>264.453</v>
       </c>
       <c r="G4">
         <v>324.9</v>
@@ -1621,28 +1621,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M4">
-        <v>8.867990600000001</v>
+        <v>13.3019859</v>
       </c>
       <c r="N4">
-        <v>774.8320093999999</v>
+        <v>770.3980141</v>
       </c>
       <c r="O4">
-        <v>232.44960282</v>
+        <v>231.11940423</v>
       </c>
       <c r="P4">
-        <v>542.38240658</v>
+        <v>539.27860987</v>
       </c>
       <c r="Q4">
-        <v>936.7824065799999</v>
+        <v>933.6786098699999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08020221276935499</v>
+        <v>0.08045197473225141</v>
       </c>
       <c r="T4">
-        <v>0.5005941136154841</v>
+        <v>0.5042284545013233</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>88.37402240818793</v>
+        <v>58.91601493879196</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07909471549028387</v>
+        <v>0.07888706246659986</v>
       </c>
       <c r="C5">
-        <v>8426.205290284774</v>
+        <v>8368.282401312617</v>
       </c>
       <c r="D5">
-        <v>8365.758290284773</v>
+        <v>8395.986401312617</v>
       </c>
       <c r="E5">
-        <v>-1722.247</v>
+        <v>-1634.096</v>
       </c>
       <c r="F5">
-        <v>264.453</v>
+        <v>352.604</v>
       </c>
       <c r="G5">
         <v>324.9</v>
@@ -1703,28 +1703,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M5">
-        <v>13.3019859</v>
+        <v>17.7359812</v>
       </c>
       <c r="N5">
-        <v>770.3980141</v>
+        <v>765.9640188</v>
       </c>
       <c r="O5">
-        <v>231.11940423</v>
+        <v>229.78920564</v>
       </c>
       <c r="P5">
-        <v>539.27860987</v>
+        <v>536.17481316</v>
       </c>
       <c r="Q5">
-        <v>933.6786098699999</v>
+        <v>930.57481316</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08045197473225141</v>
+        <v>0.08070694006937486</v>
       </c>
       <c r="T5">
-        <v>0.5042284545013233</v>
+        <v>0.507938510822284</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.91601493879196</v>
+        <v>44.18701120409396</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07888706246659986</v>
+        <v>0.07867940944291585</v>
       </c>
       <c r="C6">
-        <v>8368.282401312617</v>
+        <v>8310.578751831334</v>
       </c>
       <c r="D6">
-        <v>8395.986401312617</v>
+        <v>8426.433751831333</v>
       </c>
       <c r="E6">
-        <v>-1634.096</v>
+        <v>-1545.945</v>
       </c>
       <c r="F6">
-        <v>352.604</v>
+        <v>440.7550000000001</v>
       </c>
       <c r="G6">
         <v>324.9</v>
@@ -1785,28 +1785,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M6">
-        <v>17.7359812</v>
+        <v>22.1699765</v>
       </c>
       <c r="N6">
-        <v>765.9640188</v>
+        <v>761.5300235</v>
       </c>
       <c r="O6">
-        <v>229.78920564</v>
+        <v>228.45900705</v>
       </c>
       <c r="P6">
-        <v>536.17481316</v>
+        <v>533.07101645</v>
       </c>
       <c r="Q6">
-        <v>930.57481316</v>
+        <v>927.47101645</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08070694006937486</v>
+        <v>0.08096727309780616</v>
       </c>
       <c r="T6">
-        <v>0.507938510822284</v>
+        <v>0.5117266735921071</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.18701120409396</v>
+        <v>35.34960896327517</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07867940944291585</v>
+        <v>0.07847175641923185</v>
       </c>
       <c r="C7">
-        <v>8310.578751831334</v>
+        <v>8253.096735683648</v>
       </c>
       <c r="D7">
-        <v>8426.433751831333</v>
+        <v>8457.102735683649</v>
       </c>
       <c r="E7">
-        <v>-1545.945</v>
+        <v>-1457.794</v>
       </c>
       <c r="F7">
-        <v>440.7550000000001</v>
+        <v>528.9060000000001</v>
       </c>
       <c r="G7">
         <v>324.9</v>
@@ -1867,28 +1867,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M7">
-        <v>22.1699765</v>
+        <v>26.6039718</v>
       </c>
       <c r="N7">
-        <v>761.5300235</v>
+        <v>757.0960282</v>
       </c>
       <c r="O7">
-        <v>228.45900705</v>
+        <v>227.12880846</v>
       </c>
       <c r="P7">
-        <v>533.07101645</v>
+        <v>529.96721974</v>
       </c>
       <c r="Q7">
-        <v>927.47101645</v>
+        <v>924.36721974</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08096727309780616</v>
+        <v>0.08123314512684239</v>
       </c>
       <c r="T7">
-        <v>0.5117266735921071</v>
+        <v>0.5155954355697988</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.34960896327517</v>
+        <v>29.45800746939598</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07847175641923185</v>
+        <v>0.07826410339554785</v>
       </c>
       <c r="C8">
-        <v>8253.096735683648</v>
+        <v>8195.838781690285</v>
       </c>
       <c r="D8">
-        <v>8457.102735683649</v>
+        <v>8487.995781690286</v>
       </c>
       <c r="E8">
-        <v>-1457.794</v>
+        <v>-1369.643</v>
       </c>
       <c r="F8">
-        <v>528.9059999999999</v>
+        <v>617.057</v>
       </c>
       <c r="G8">
         <v>324.9</v>
@@ -1949,28 +1949,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M8">
-        <v>26.6039718</v>
+        <v>31.0379671</v>
       </c>
       <c r="N8">
-        <v>757.0960282</v>
+        <v>752.6620329</v>
       </c>
       <c r="O8">
-        <v>227.12880846</v>
+        <v>225.79860987</v>
       </c>
       <c r="P8">
-        <v>529.96721974</v>
+        <v>526.86342303</v>
       </c>
       <c r="Q8">
-        <v>924.36721974</v>
+        <v>921.26342303</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08123314512684239</v>
+        <v>0.08150473483392241</v>
       </c>
       <c r="T8">
-        <v>0.5155954355697988</v>
+        <v>0.5195473967298065</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.45800746939598</v>
+        <v>25.2497206880537</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07826410339554783</v>
+        <v>0.07805645037186383</v>
       </c>
       <c r="C9">
-        <v>8195.838781690287</v>
+        <v>8138.807354291137</v>
       </c>
       <c r="D9">
-        <v>8487.995781690288</v>
+        <v>8519.115354291138</v>
       </c>
       <c r="E9">
-        <v>-1369.643</v>
+        <v>-1281.492</v>
       </c>
       <c r="F9">
-        <v>617.0570000000001</v>
+        <v>705.2080000000001</v>
       </c>
       <c r="G9">
         <v>324.9</v>
@@ -2031,28 +2031,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M9">
-        <v>31.03796710000001</v>
+        <v>35.4719624</v>
       </c>
       <c r="N9">
-        <v>752.6620328999999</v>
+        <v>748.2280375999999</v>
       </c>
       <c r="O9">
-        <v>225.79860987</v>
+        <v>224.46841128</v>
       </c>
       <c r="P9">
-        <v>526.8634230299999</v>
+        <v>523.7596263199999</v>
       </c>
       <c r="Q9">
-        <v>921.2634230299999</v>
+        <v>918.1596263199999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08150473483392241</v>
+        <v>0.08178222866506939</v>
       </c>
       <c r="T9">
-        <v>0.5195473967298065</v>
+        <v>0.5235852700889448</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.24972068805369</v>
+        <v>22.09350560204698</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07805645037186383</v>
+        <v>0.07784879734817983</v>
       </c>
       <c r="C10">
-        <v>8138.807354291137</v>
+        <v>8082.004954200635</v>
       </c>
       <c r="D10">
-        <v>8519.115354291138</v>
+        <v>8550.463954200635</v>
       </c>
       <c r="E10">
-        <v>-1281.492</v>
+        <v>-1193.341</v>
       </c>
       <c r="F10">
-        <v>705.2080000000001</v>
+        <v>793.359</v>
       </c>
       <c r="G10">
         <v>324.9</v>
@@ -2113,28 +2113,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M10">
-        <v>35.4719624</v>
+        <v>39.9059577</v>
       </c>
       <c r="N10">
-        <v>748.2280375999999</v>
+        <v>743.7940422999999</v>
       </c>
       <c r="O10">
-        <v>224.46841128</v>
+        <v>223.13821269</v>
       </c>
       <c r="P10">
-        <v>523.7596263199999</v>
+        <v>520.65582961</v>
       </c>
       <c r="Q10">
-        <v>918.1596263199999</v>
+        <v>915.0558296099999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08178222866506939</v>
+        <v>0.08206582126173607</v>
       </c>
       <c r="T10">
-        <v>0.5235852700889448</v>
+        <v>0.5277118879175147</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.09350560204698</v>
+        <v>19.63867164626398</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07784879734817983</v>
+        <v>0.07764114432449581</v>
       </c>
       <c r="C11">
-        <v>8082.004954200635</v>
+        <v>8025.434119077625</v>
       </c>
       <c r="D11">
-        <v>8550.463954200635</v>
+        <v>8582.044119077626</v>
       </c>
       <c r="E11">
-        <v>-1193.341</v>
+        <v>-1105.19</v>
       </c>
       <c r="F11">
-        <v>793.359</v>
+        <v>881.51</v>
       </c>
       <c r="G11">
         <v>324.9</v>
@@ -2195,28 +2195,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M11">
-        <v>39.9059577</v>
+        <v>44.33995299999999</v>
       </c>
       <c r="N11">
-        <v>743.7940422999999</v>
+        <v>739.3600469999999</v>
       </c>
       <c r="O11">
-        <v>223.13821269</v>
+        <v>221.8080141</v>
       </c>
       <c r="P11">
-        <v>520.65582961</v>
+        <v>517.5520329</v>
       </c>
       <c r="Q11">
-        <v>915.0558296099999</v>
+        <v>911.9520328999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08206582126173607</v>
+        <v>0.08235571591610646</v>
       </c>
       <c r="T11">
-        <v>0.5277118879175147</v>
+        <v>0.5319302083644971</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.63867164626398</v>
+        <v>17.67480448163759</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07764114432449581</v>
+        <v>0.07743349130081181</v>
       </c>
       <c r="C12">
-        <v>8025.434119077625</v>
+        <v>7969.097424210151</v>
       </c>
       <c r="D12">
-        <v>8582.044119077626</v>
+        <v>8613.858424210151</v>
       </c>
       <c r="E12">
-        <v>-1105.19</v>
+        <v>-1017.039</v>
       </c>
       <c r="F12">
-        <v>881.5100000000001</v>
+        <v>969.6610000000001</v>
       </c>
       <c r="G12">
         <v>324.9</v>
@@ -2277,28 +2277,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M12">
-        <v>44.339953</v>
+        <v>48.7739483</v>
       </c>
       <c r="N12">
-        <v>739.3600469999999</v>
+        <v>734.9260516999999</v>
       </c>
       <c r="O12">
-        <v>221.8080141</v>
+        <v>220.47781551</v>
       </c>
       <c r="P12">
-        <v>517.5520329</v>
+        <v>514.44823619</v>
       </c>
       <c r="Q12">
-        <v>911.9520328999999</v>
+        <v>908.84823619</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08235571591610646</v>
+        <v>0.08265212505709192</v>
       </c>
       <c r="T12">
-        <v>0.5319302083644971</v>
+        <v>0.5362433225293894</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.67480448163758</v>
+        <v>16.06800407421598</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07743349130081181</v>
+        <v>0.0772258382771278</v>
       </c>
       <c r="C13">
-        <v>7969.097424210151</v>
+        <v>7912.997483215519</v>
       </c>
       <c r="D13">
-        <v>8613.858424210151</v>
+        <v>8645.909483215519</v>
       </c>
       <c r="E13">
-        <v>-1017.039</v>
+        <v>-928.8880000000004</v>
       </c>
       <c r="F13">
-        <v>969.6610000000001</v>
+        <v>1057.812</v>
       </c>
       <c r="G13">
         <v>324.9</v>
@@ -2359,28 +2359,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M13">
-        <v>48.7739483</v>
+        <v>53.20794359999999</v>
       </c>
       <c r="N13">
-        <v>734.9260516999999</v>
+        <v>730.4920563999999</v>
       </c>
       <c r="O13">
-        <v>220.47781551</v>
+        <v>219.14761692</v>
       </c>
       <c r="P13">
-        <v>514.44823619</v>
+        <v>511.3444394799999</v>
       </c>
       <c r="Q13">
-        <v>908.84823619</v>
+        <v>905.74443948</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08265212505709192</v>
+        <v>0.08295527076946341</v>
       </c>
       <c r="T13">
-        <v>0.5362433225293894</v>
+        <v>0.540654462016211</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.06800407421598</v>
+        <v>14.72900373469799</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0772258382771278</v>
+        <v>0.0770181852534438</v>
       </c>
       <c r="C14">
-        <v>7912.997483215519</v>
+        <v>7857.136948756048</v>
       </c>
       <c r="D14">
-        <v>8645.909483215519</v>
+        <v>8678.199948756048</v>
       </c>
       <c r="E14">
-        <v>-928.8880000000004</v>
+        <v>-840.7370000000001</v>
       </c>
       <c r="F14">
-        <v>1057.812</v>
+        <v>1145.963</v>
       </c>
       <c r="G14">
         <v>324.9</v>
@@ -2441,28 +2441,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M14">
-        <v>53.20794359999999</v>
+        <v>57.64193890000001</v>
       </c>
       <c r="N14">
-        <v>730.4920563999999</v>
+        <v>726.0580610999999</v>
       </c>
       <c r="O14">
-        <v>219.14761692</v>
+        <v>217.81741833</v>
       </c>
       <c r="P14">
-        <v>511.3444394799999</v>
+        <v>508.2406427699999</v>
       </c>
       <c r="Q14">
-        <v>905.74443948</v>
+        <v>902.6406427699999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08295527076946341</v>
+        <v>0.08326538534878597</v>
       </c>
       <c r="T14">
-        <v>0.540654462016211</v>
+        <v>0.5451670070084769</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.72900373469799</v>
+        <v>13.59600344741353</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0770181852534438</v>
+        <v>0.0768105322297598</v>
       </c>
       <c r="C15">
-        <v>7857.136948756048</v>
+        <v>7801.518513270929</v>
       </c>
       <c r="D15">
-        <v>8678.199948756048</v>
+        <v>8710.73251327093</v>
       </c>
       <c r="E15">
-        <v>-840.7370000000001</v>
+        <v>-752.586</v>
       </c>
       <c r="F15">
-        <v>1145.963</v>
+        <v>1234.114</v>
       </c>
       <c r="G15">
         <v>324.9</v>
@@ -2523,28 +2523,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M15">
-        <v>57.64193890000001</v>
+        <v>62.07593420000001</v>
       </c>
       <c r="N15">
-        <v>726.0580610999999</v>
+        <v>721.6240657999999</v>
       </c>
       <c r="O15">
-        <v>217.81741833</v>
+        <v>216.48721974</v>
       </c>
       <c r="P15">
-        <v>508.2406427699999</v>
+        <v>505.1368460599999</v>
       </c>
       <c r="Q15">
-        <v>902.6406427699999</v>
+        <v>899.5368460599999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08326538534878597</v>
+        <v>0.08358271189506952</v>
       </c>
       <c r="T15">
-        <v>0.5451670070084769</v>
+        <v>0.5497844949075394</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.59600344741353</v>
+        <v>12.62486034402684</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0768105322297598</v>
+        <v>0.07660287920607577</v>
       </c>
       <c r="C16">
-        <v>7801.518513270929</v>
+        <v>7746.144909724607</v>
       </c>
       <c r="D16">
-        <v>8710.73251327093</v>
+        <v>8743.509909724607</v>
       </c>
       <c r="E16">
-        <v>-752.586</v>
+        <v>-664.4349999999999</v>
       </c>
       <c r="F16">
-        <v>1234.114</v>
+        <v>1322.265</v>
       </c>
       <c r="G16">
         <v>324.9</v>
@@ -2605,28 +2605,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M16">
-        <v>62.07593420000001</v>
+        <v>66.50992950000001</v>
       </c>
       <c r="N16">
-        <v>721.6240657999999</v>
+        <v>717.1900704999999</v>
       </c>
       <c r="O16">
-        <v>216.48721974</v>
+        <v>215.15702115</v>
       </c>
       <c r="P16">
-        <v>505.1368460599999</v>
+        <v>502.0330493499999</v>
       </c>
       <c r="Q16">
-        <v>899.5368460599999</v>
+        <v>896.4330493499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08358271189506952</v>
+        <v>0.08390750494832444</v>
       </c>
       <c r="T16">
-        <v>0.5497844949075394</v>
+        <v>0.5545106295806977</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.62486034402684</v>
+        <v>11.78320298775839</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07660287920607577</v>
+        <v>0.07639522618239176</v>
       </c>
       <c r="C17">
-        <v>7746.144909724607</v>
+        <v>7691.018912372095</v>
       </c>
       <c r="D17">
-        <v>8743.509909724607</v>
+        <v>8776.534912372095</v>
       </c>
       <c r="E17">
-        <v>-664.4350000000002</v>
+        <v>-576.2840000000001</v>
       </c>
       <c r="F17">
-        <v>1322.265</v>
+        <v>1410.416</v>
       </c>
       <c r="G17">
         <v>324.9</v>
@@ -2687,28 +2687,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M17">
-        <v>66.5099295</v>
+        <v>70.9439248</v>
       </c>
       <c r="N17">
-        <v>717.1900704999999</v>
+        <v>712.7560751999999</v>
       </c>
       <c r="O17">
-        <v>215.15702115</v>
+        <v>213.82682256</v>
       </c>
       <c r="P17">
-        <v>502.0330493499999</v>
+        <v>498.92925264</v>
       </c>
       <c r="Q17">
-        <v>896.4330493499999</v>
+        <v>893.3292526399999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08390750494832444</v>
+        <v>0.08424003116951401</v>
       </c>
       <c r="T17">
-        <v>0.5545106295806977</v>
+        <v>0.5593492912698836</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.78320298775839</v>
+        <v>11.04675280102349</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07639522618239176</v>
+        <v>0.07618757315870776</v>
       </c>
       <c r="C18">
-        <v>7691.018912372095</v>
+        <v>7636.14333754175</v>
       </c>
       <c r="D18">
-        <v>8776.534912372095</v>
+        <v>8809.81033754175</v>
       </c>
       <c r="E18">
-        <v>-576.2840000000001</v>
+        <v>-488.133</v>
       </c>
       <c r="F18">
-        <v>1410.416</v>
+        <v>1498.567</v>
       </c>
       <c r="G18">
         <v>324.9</v>
@@ -2769,28 +2769,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M18">
-        <v>70.9439248</v>
+        <v>75.37792010000001</v>
       </c>
       <c r="N18">
-        <v>712.7560751999999</v>
+        <v>708.3220798999999</v>
       </c>
       <c r="O18">
-        <v>213.82682256</v>
+        <v>212.49662397</v>
       </c>
       <c r="P18">
-        <v>498.92925264</v>
+        <v>495.82545593</v>
       </c>
       <c r="Q18">
-        <v>893.3292526399999</v>
+        <v>890.22545593</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08424003116951401</v>
+        <v>0.08458057007073225</v>
       </c>
       <c r="T18">
-        <v>0.5593492912698836</v>
+        <v>0.5643045472166403</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.04675280102349</v>
+        <v>10.39694381272799</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07618757315870776</v>
+        <v>0.07597992013502376</v>
       </c>
       <c r="C19">
-        <v>7636.14333754175</v>
+        <v>7581.521044435876</v>
       </c>
       <c r="D19">
-        <v>8809.81033754175</v>
+        <v>8843.339044435877</v>
       </c>
       <c r="E19">
-        <v>-488.133</v>
+        <v>-399.982</v>
       </c>
       <c r="F19">
-        <v>1498.567</v>
+        <v>1586.718</v>
       </c>
       <c r="G19">
         <v>324.9</v>
@@ -2851,28 +2851,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M19">
-        <v>75.37792010000001</v>
+        <v>79.81191540000002</v>
       </c>
       <c r="N19">
-        <v>708.3220798999999</v>
+        <v>703.8880846</v>
       </c>
       <c r="O19">
-        <v>212.49662397</v>
+        <v>211.16642538</v>
       </c>
       <c r="P19">
-        <v>495.82545593</v>
+        <v>492.72165922</v>
       </c>
       <c r="Q19">
-        <v>890.22545593</v>
+        <v>887.12165922</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08458057007073225</v>
+        <v>0.08492941479880946</v>
       </c>
       <c r="T19">
-        <v>0.5643045472166403</v>
+        <v>0.5693806630645372</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.39694381272799</v>
+        <v>9.81933582313199</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07597992013502376</v>
+        <v>0.07577226711133975</v>
       </c>
       <c r="C20">
-        <v>7581.521044435877</v>
+        <v>7527.154935949715</v>
       </c>
       <c r="D20">
-        <v>8843.339044435877</v>
+        <v>8877.123935949716</v>
       </c>
       <c r="E20">
-        <v>-399.9820000000002</v>
+        <v>-311.8310000000001</v>
       </c>
       <c r="F20">
-        <v>1586.718</v>
+        <v>1674.869</v>
       </c>
       <c r="G20">
         <v>324.9</v>
@@ -2933,28 +2933,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M20">
-        <v>79.8119154</v>
+        <v>84.2459107</v>
       </c>
       <c r="N20">
-        <v>703.8880846</v>
+        <v>699.4540893</v>
       </c>
       <c r="O20">
-        <v>211.16642538</v>
+        <v>209.83622679</v>
       </c>
       <c r="P20">
-        <v>492.72165922</v>
+        <v>489.61786251</v>
       </c>
       <c r="Q20">
-        <v>887.12165922</v>
+        <v>884.01786251</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08492941479880946</v>
+        <v>0.08528687297696265</v>
       </c>
       <c r="T20">
-        <v>0.5693806630645372</v>
+        <v>0.5745821151062094</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.819335823131992</v>
+        <v>9.3025286745461</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07577226711133975</v>
+        <v>0.07556461408765575</v>
       </c>
       <c r="C21">
-        <v>7527.154935949715</v>
+        <v>7473.047959509235</v>
       </c>
       <c r="D21">
-        <v>8877.123935949716</v>
+        <v>8911.167959509236</v>
       </c>
       <c r="E21">
-        <v>-311.8310000000001</v>
+        <v>-223.6800000000001</v>
       </c>
       <c r="F21">
-        <v>1674.869</v>
+        <v>1763.02</v>
       </c>
       <c r="G21">
         <v>324.9</v>
@@ -3015,28 +3015,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M21">
-        <v>84.2459107</v>
+        <v>88.679906</v>
       </c>
       <c r="N21">
-        <v>699.4540893</v>
+        <v>695.020094</v>
       </c>
       <c r="O21">
-        <v>209.83622679</v>
+        <v>208.5060282</v>
       </c>
       <c r="P21">
-        <v>489.61786251</v>
+        <v>486.5140658</v>
       </c>
       <c r="Q21">
-        <v>884.01786251</v>
+        <v>880.9140658</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08528687297696265</v>
+        <v>0.08565326760956968</v>
       </c>
       <c r="T21">
-        <v>0.5745821151062094</v>
+        <v>0.5799136034489235</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.3025286745461</v>
+        <v>8.837402240818793</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07556461408765575</v>
+        <v>0.07557746106397173</v>
       </c>
       <c r="C22">
-        <v>7473.047959509235</v>
+        <v>7382.783164527056</v>
       </c>
       <c r="D22">
-        <v>8911.167959509236</v>
+        <v>8909.054164527057</v>
       </c>
       <c r="E22">
-        <v>-223.6800000000001</v>
+        <v>-135.529</v>
       </c>
       <c r="F22">
-        <v>1763.02</v>
+        <v>1851.171</v>
       </c>
       <c r="G22">
         <v>324.9</v>
@@ -3097,45 +3097,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M22">
-        <v>88.679906</v>
+        <v>95.89065780000001</v>
       </c>
       <c r="N22">
-        <v>695.020094</v>
+        <v>687.8093421999999</v>
       </c>
       <c r="O22">
-        <v>208.5060282</v>
+        <v>206.34280266</v>
       </c>
       <c r="P22">
-        <v>486.5140658</v>
+        <v>481.46653954</v>
       </c>
       <c r="Q22">
-        <v>880.9140658</v>
+        <v>875.86653954</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08565326760956968</v>
+        <v>0.08602893805566042</v>
       </c>
       <c r="T22">
-        <v>0.5799136034489235</v>
+        <v>0.5853800661800607</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>8.837402240818793</v>
+        <v>8.172850390019953</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07557746106397173</v>
+        <v>0.07538030804028772</v>
       </c>
       <c r="C23">
-        <v>7382.783164527056</v>
+        <v>7327.181803393571</v>
       </c>
       <c r="D23">
-        <v>8909.054164527057</v>
+        <v>8941.603803393571</v>
       </c>
       <c r="E23">
-        <v>-135.5290000000002</v>
+        <v>-47.37800000000016</v>
       </c>
       <c r="F23">
-        <v>1851.171</v>
+        <v>1939.322</v>
       </c>
       <c r="G23">
         <v>324.9</v>
@@ -3179,28 +3179,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M23">
-        <v>95.8906578</v>
+        <v>100.4568796</v>
       </c>
       <c r="N23">
-        <v>687.8093421999999</v>
+        <v>683.2431204</v>
       </c>
       <c r="O23">
-        <v>206.34280266</v>
+        <v>204.97293612</v>
       </c>
       <c r="P23">
-        <v>481.46653954</v>
+        <v>478.27018428</v>
       </c>
       <c r="Q23">
-        <v>875.86653954</v>
+        <v>872.6701842799999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08602893805566042</v>
+        <v>0.08641424107729195</v>
       </c>
       <c r="T23">
-        <v>0.5853800661800606</v>
+        <v>0.5909866946222526</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.172850390019953</v>
+        <v>7.801357190473592</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07538030804028772</v>
+        <v>0.07518315501660372</v>
       </c>
       <c r="C24">
-        <v>7327.181803393571</v>
+        <v>7271.819157620906</v>
       </c>
       <c r="D24">
-        <v>8941.603803393571</v>
+        <v>8974.392157620907</v>
       </c>
       <c r="E24">
-        <v>-47.37800000000016</v>
+        <v>40.77299999999991</v>
       </c>
       <c r="F24">
-        <v>1939.322</v>
+        <v>2027.473</v>
       </c>
       <c r="G24">
         <v>324.9</v>
@@ -3261,28 +3261,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M24">
-        <v>100.4568796</v>
+        <v>105.0231014</v>
       </c>
       <c r="N24">
-        <v>683.2431204</v>
+        <v>678.6768986</v>
       </c>
       <c r="O24">
-        <v>204.97293612</v>
+        <v>203.60306958</v>
       </c>
       <c r="P24">
-        <v>478.27018428</v>
+        <v>475.0738290199999</v>
       </c>
       <c r="Q24">
-        <v>872.6701842799999</v>
+        <v>869.4738290199999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08641424107729195</v>
+        <v>0.08680955196961522</v>
       </c>
       <c r="T24">
-        <v>0.5909866946222526</v>
+        <v>0.5967389497772287</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.801357190473592</v>
+        <v>7.462167747409524</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07518315501660372</v>
+        <v>0.07498600199291972</v>
       </c>
       <c r="C25">
-        <v>7271.819157620906</v>
+        <v>7216.69786294123</v>
       </c>
       <c r="D25">
-        <v>8974.392157620907</v>
+        <v>9007.42186294123</v>
       </c>
       <c r="E25">
-        <v>40.77299999999991</v>
+        <v>128.924</v>
       </c>
       <c r="F25">
-        <v>2027.473</v>
+        <v>2115.624</v>
       </c>
       <c r="G25">
         <v>324.9</v>
@@ -3343,28 +3343,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M25">
-        <v>105.0231014</v>
+        <v>109.5893232</v>
       </c>
       <c r="N25">
-        <v>678.6768986</v>
+        <v>674.1106768</v>
       </c>
       <c r="O25">
-        <v>203.60306958</v>
+        <v>202.23320304</v>
       </c>
       <c r="P25">
-        <v>475.0738290199999</v>
+        <v>471.87747376</v>
       </c>
       <c r="Q25">
-        <v>869.4738290199999</v>
+        <v>866.27747376</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08680955196961522</v>
+        <v>0.08721526578015752</v>
       </c>
       <c r="T25">
-        <v>0.5967389497772287</v>
+        <v>0.6026425800678623</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.462167747409524</v>
+        <v>7.15124409126746</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07498600199291972</v>
+        <v>0.0747888489692357</v>
       </c>
       <c r="C26">
-        <v>7216.69786294123</v>
+        <v>7161.820594032655</v>
       </c>
       <c r="D26">
-        <v>9007.42186294123</v>
+        <v>9040.695594032655</v>
       </c>
       <c r="E26">
-        <v>128.9239999999995</v>
+        <v>217.0749999999998</v>
       </c>
       <c r="F26">
-        <v>2115.624</v>
+        <v>2203.775</v>
       </c>
       <c r="G26">
         <v>324.9</v>
@@ -3425,28 +3425,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M26">
-        <v>109.5893232</v>
+        <v>114.155545</v>
       </c>
       <c r="N26">
-        <v>674.1106768</v>
+        <v>669.544455</v>
       </c>
       <c r="O26">
-        <v>202.23320304</v>
+        <v>200.8633365</v>
       </c>
       <c r="P26">
-        <v>471.87747376</v>
+        <v>468.6811185</v>
       </c>
       <c r="Q26">
-        <v>866.27747376</v>
+        <v>863.0811185</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08721526578015752</v>
+        <v>0.0876317986256476</v>
       </c>
       <c r="T26">
-        <v>0.6026425800678623</v>
+        <v>0.6087036404995793</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.151244091267461</v>
+        <v>6.865194327616761</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0747888489692357</v>
+        <v>0.07490109594555169</v>
       </c>
       <c r="C27">
-        <v>7161.820594032655</v>
+        <v>7054.695474905401</v>
       </c>
       <c r="D27">
-        <v>9040.695594032655</v>
+        <v>9021.721474905402</v>
       </c>
       <c r="E27">
-        <v>217.0749999999998</v>
+        <v>305.2260000000001</v>
       </c>
       <c r="F27">
-        <v>2203.775</v>
+        <v>2291.926</v>
       </c>
       <c r="G27">
         <v>324.9</v>
@@ -3507,45 +3507,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M27">
-        <v>114.155545</v>
+        <v>122.618041</v>
       </c>
       <c r="N27">
-        <v>669.544455</v>
+        <v>661.0819589999999</v>
       </c>
       <c r="O27">
-        <v>200.8633365</v>
+        <v>198.3245877</v>
       </c>
       <c r="P27">
-        <v>468.6811185</v>
+        <v>462.7573712999999</v>
       </c>
       <c r="Q27">
-        <v>863.0811185</v>
+        <v>857.1573712999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0876317986256476</v>
+        <v>0.0880595891156104</v>
       </c>
       <c r="T27">
-        <v>0.6087036404995793</v>
+        <v>0.6149285133753967</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.865194327616761</v>
+        <v>6.391392274812152</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07490109594555169</v>
+        <v>0.07471584292186768</v>
       </c>
       <c r="C28">
-        <v>7054.695474905401</v>
+        <v>6997.902359550472</v>
       </c>
       <c r="D28">
-        <v>9021.721474905402</v>
+        <v>9053.079359550473</v>
       </c>
       <c r="E28">
-        <v>305.2260000000001</v>
+        <v>393.377</v>
       </c>
       <c r="F28">
-        <v>2291.926</v>
+        <v>2380.077</v>
       </c>
       <c r="G28">
         <v>324.9</v>
@@ -3589,28 +3589,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M28">
-        <v>122.618041</v>
+        <v>127.3341195</v>
       </c>
       <c r="N28">
-        <v>661.0819589999999</v>
+        <v>656.3658804999999</v>
       </c>
       <c r="O28">
-        <v>198.3245877</v>
+        <v>196.90976415</v>
       </c>
       <c r="P28">
-        <v>462.7573712999999</v>
+        <v>459.4561163499999</v>
       </c>
       <c r="Q28">
-        <v>857.1573712999999</v>
+        <v>853.8561163499999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0880595891156104</v>
+        <v>0.08849909989296945</v>
       </c>
       <c r="T28">
-        <v>0.6149285133753967</v>
+        <v>0.6213239307135654</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.391392274812152</v>
+        <v>6.154674042411703</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07471584292186768</v>
+        <v>0.07453058989818367</v>
       </c>
       <c r="C29">
-        <v>6997.902359550472</v>
+        <v>6941.327993286064</v>
       </c>
       <c r="D29">
-        <v>9053.079359550473</v>
+        <v>9084.655993286065</v>
       </c>
       <c r="E29">
-        <v>393.377</v>
+        <v>481.5280000000002</v>
       </c>
       <c r="F29">
-        <v>2380.077</v>
+        <v>2468.228000000001</v>
       </c>
       <c r="G29">
         <v>324.9</v>
@@ -3671,28 +3671,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M29">
-        <v>127.3341195</v>
+        <v>132.050198</v>
       </c>
       <c r="N29">
-        <v>656.3658804999999</v>
+        <v>651.6498019999999</v>
       </c>
       <c r="O29">
-        <v>196.90976415</v>
+        <v>195.4949406</v>
       </c>
       <c r="P29">
-        <v>459.4561163499999</v>
+        <v>456.1548614</v>
       </c>
       <c r="Q29">
-        <v>853.8561163499999</v>
+        <v>850.5548613999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08849909989296945</v>
+        <v>0.08895081930303289</v>
       </c>
       <c r="T29">
-        <v>0.6213239307135654</v>
+        <v>0.6278969985333497</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.154674042411703</v>
+        <v>5.934864255182713</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07453058989818367</v>
+        <v>0.07434533687449967</v>
       </c>
       <c r="C30">
-        <v>6941.327993286064</v>
+        <v>6884.974673077591</v>
       </c>
       <c r="D30">
-        <v>9084.655993286065</v>
+        <v>9116.453673077593</v>
       </c>
       <c r="E30">
-        <v>481.5280000000002</v>
+        <v>569.6790000000001</v>
       </c>
       <c r="F30">
-        <v>2468.228000000001</v>
+        <v>2556.379</v>
       </c>
       <c r="G30">
         <v>324.9</v>
@@ -3753,28 +3753,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M30">
-        <v>132.050198</v>
+        <v>136.7662765</v>
       </c>
       <c r="N30">
-        <v>651.6498019999999</v>
+        <v>646.9337234999999</v>
       </c>
       <c r="O30">
-        <v>195.4949406</v>
+        <v>194.08011705</v>
       </c>
       <c r="P30">
-        <v>456.1548614</v>
+        <v>452.8536064499999</v>
       </c>
       <c r="Q30">
-        <v>850.5548613999999</v>
+        <v>847.2536064499999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08895081930303289</v>
+        <v>0.08941526320352067</v>
       </c>
       <c r="T30">
-        <v>0.6278969985333497</v>
+        <v>0.6346552231931282</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.934864255182713</v>
+        <v>5.73021376362469</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07434533687449967</v>
+        <v>0.07432808385081566</v>
       </c>
       <c r="C31">
-        <v>6884.974673077592</v>
+        <v>6799.796395649031</v>
       </c>
       <c r="D31">
-        <v>9116.453673077593</v>
+        <v>9119.426395649032</v>
       </c>
       <c r="E31">
-        <v>569.6789999999996</v>
+        <v>657.8299999999999</v>
       </c>
       <c r="F31">
-        <v>2556.379</v>
+        <v>2644.53</v>
       </c>
       <c r="G31">
         <v>324.9</v>
@@ -3835,45 +3835,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M31">
-        <v>136.7662765</v>
+        <v>143.597979</v>
       </c>
       <c r="N31">
-        <v>646.9337234999999</v>
+        <v>640.1020209999999</v>
       </c>
       <c r="O31">
-        <v>194.08011705</v>
+        <v>192.0306063</v>
       </c>
       <c r="P31">
-        <v>452.8536064499999</v>
+        <v>448.0714147</v>
       </c>
       <c r="Q31">
-        <v>847.2536064499999</v>
+        <v>842.4714147</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08941526320352067</v>
+        <v>0.08989297692973666</v>
       </c>
       <c r="T31">
-        <v>0.6346552231931282</v>
+        <v>0.641606539986043</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>5.73021376362469</v>
+        <v>5.457597700591593</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07432808385081566</v>
+        <v>0.07414843082713164</v>
       </c>
       <c r="C32">
-        <v>6799.796395649031</v>
+        <v>6742.715479273611</v>
       </c>
       <c r="D32">
-        <v>9119.426395649032</v>
+        <v>9150.496479273612</v>
       </c>
       <c r="E32">
-        <v>657.8299999999999</v>
+        <v>745.9809999999998</v>
       </c>
       <c r="F32">
-        <v>2644.53</v>
+        <v>2732.681</v>
       </c>
       <c r="G32">
         <v>324.9</v>
@@ -3917,28 +3917,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M32">
-        <v>143.597979</v>
+        <v>148.3845783</v>
       </c>
       <c r="N32">
-        <v>640.1020209999999</v>
+        <v>635.3154216999999</v>
       </c>
       <c r="O32">
-        <v>192.0306063</v>
+        <v>190.59462651</v>
       </c>
       <c r="P32">
-        <v>448.0714147</v>
+        <v>444.7207951899999</v>
       </c>
       <c r="Q32">
-        <v>842.4714147</v>
+        <v>839.1207951899999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08989297692973666</v>
+        <v>0.09038453743062558</v>
       </c>
       <c r="T32">
-        <v>0.641606539986043</v>
+        <v>0.6487593442222307</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.457597700591593</v>
+        <v>5.281546161862832</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07414843082713164</v>
+        <v>0.07396877780344764</v>
       </c>
       <c r="C33">
-        <v>6742.715479273611</v>
+        <v>6685.84699957283</v>
       </c>
       <c r="D33">
-        <v>9150.496479273612</v>
+        <v>9181.778999572831</v>
       </c>
       <c r="E33">
-        <v>745.9809999999998</v>
+        <v>834.1320000000001</v>
       </c>
       <c r="F33">
-        <v>2732.681</v>
+        <v>2820.832</v>
       </c>
       <c r="G33">
         <v>324.9</v>
@@ -3999,28 +3999,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M33">
-        <v>148.3845783</v>
+        <v>153.1711776</v>
       </c>
       <c r="N33">
-        <v>635.3154216999999</v>
+        <v>630.5288223999999</v>
       </c>
       <c r="O33">
-        <v>190.59462651</v>
+        <v>189.15864672</v>
       </c>
       <c r="P33">
-        <v>444.7207951899999</v>
+        <v>441.3701756799999</v>
       </c>
       <c r="Q33">
-        <v>839.1207951899999</v>
+        <v>835.7701756799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09038453743062558</v>
+        <v>0.09089055559330536</v>
       </c>
       <c r="T33">
-        <v>0.6487593442222307</v>
+        <v>0.6561225250536005</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.281546161862832</v>
+        <v>5.116497844304618</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07396877780344764</v>
+        <v>0.07378912477976364</v>
       </c>
       <c r="C34">
-        <v>6685.84699957283</v>
+        <v>6629.19314277281</v>
       </c>
       <c r="D34">
-        <v>9181.778999572831</v>
+        <v>9213.276142772811</v>
       </c>
       <c r="E34">
-        <v>834.1320000000001</v>
+        <v>922.2829999999999</v>
       </c>
       <c r="F34">
-        <v>2820.832</v>
+        <v>2908.983</v>
       </c>
       <c r="G34">
         <v>324.9</v>
@@ -4081,28 +4081,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M34">
-        <v>153.1711776</v>
+        <v>157.9577769</v>
       </c>
       <c r="N34">
-        <v>630.5288223999999</v>
+        <v>625.7422230999999</v>
       </c>
       <c r="O34">
-        <v>189.15864672</v>
+        <v>187.72266693</v>
       </c>
       <c r="P34">
-        <v>441.3701756799999</v>
+        <v>438.01955617</v>
       </c>
       <c r="Q34">
-        <v>835.7701756799999</v>
+        <v>832.41955617</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09089055559330536</v>
+        <v>0.09141167877576664</v>
       </c>
       <c r="T34">
-        <v>0.6561225250536005</v>
+        <v>0.6637055023276979</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.116497844304618</v>
+        <v>4.961452455083267</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07378912477976364</v>
+        <v>0.07360947175607963</v>
       </c>
       <c r="C35">
-        <v>6629.19314277281</v>
+        <v>6572.756125201427</v>
       </c>
       <c r="D35">
-        <v>9213.276142772811</v>
+        <v>9244.990125201428</v>
       </c>
       <c r="E35">
-        <v>922.2829999999999</v>
+        <v>1010.434</v>
       </c>
       <c r="F35">
-        <v>2908.983</v>
+        <v>2997.134</v>
       </c>
       <c r="G35">
         <v>324.9</v>
@@ -4163,28 +4163,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M35">
-        <v>157.9577769</v>
+        <v>162.7443762</v>
       </c>
       <c r="N35">
-        <v>625.7422230999999</v>
+        <v>620.9556237999999</v>
       </c>
       <c r="O35">
-        <v>187.72266693</v>
+        <v>186.28668714</v>
       </c>
       <c r="P35">
-        <v>438.01955617</v>
+        <v>434.6689366599999</v>
       </c>
       <c r="Q35">
-        <v>832.41955617</v>
+        <v>829.06893666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09141167877576664</v>
+        <v>0.09194859356981763</v>
       </c>
       <c r="T35">
-        <v>0.6637055023276979</v>
+        <v>0.6715182667919192</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.961452455083267</v>
+        <v>4.815527382874935</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07360947175607963</v>
+        <v>0.07342981873239562</v>
       </c>
       <c r="C36">
-        <v>6572.756125201427</v>
+        <v>6516.538193808172</v>
       </c>
       <c r="D36">
-        <v>9244.990125201428</v>
+        <v>9276.923193808172</v>
       </c>
       <c r="E36">
-        <v>1010.434</v>
+        <v>1098.585</v>
       </c>
       <c r="F36">
-        <v>2997.134</v>
+        <v>3085.285</v>
       </c>
       <c r="G36">
         <v>324.9</v>
@@ -4245,28 +4245,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M36">
-        <v>162.7443762</v>
+        <v>167.5309755</v>
       </c>
       <c r="N36">
-        <v>620.9556237999999</v>
+        <v>616.1690245</v>
       </c>
       <c r="O36">
-        <v>186.28668714</v>
+        <v>184.85070735</v>
       </c>
       <c r="P36">
-        <v>434.6689366599999</v>
+        <v>431.31831715</v>
       </c>
       <c r="Q36">
-        <v>829.06893666</v>
+        <v>825.71831715</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09194859356981763</v>
+        <v>0.0925020288190702</v>
       </c>
       <c r="T36">
-        <v>0.6715182667919192</v>
+        <v>0.6795714240088858</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.815527382874935</v>
+        <v>4.677940886221366</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07342981873239562</v>
+        <v>0.07325016570871162</v>
       </c>
       <c r="C37">
-        <v>6516.538193808172</v>
+        <v>6460.541626694844</v>
       </c>
       <c r="D37">
-        <v>9276.923193808172</v>
+        <v>9309.077626694845</v>
       </c>
       <c r="E37">
-        <v>1098.585</v>
+        <v>1186.736</v>
       </c>
       <c r="F37">
-        <v>3085.285</v>
+        <v>3173.436000000001</v>
       </c>
       <c r="G37">
         <v>324.9</v>
@@ -4327,28 +4327,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M37">
-        <v>167.5309755</v>
+        <v>172.3175748</v>
       </c>
       <c r="N37">
-        <v>616.1690245</v>
+        <v>611.3824251999999</v>
       </c>
       <c r="O37">
-        <v>184.85070735</v>
+        <v>183.41472756</v>
       </c>
       <c r="P37">
-        <v>431.31831715</v>
+        <v>427.96769764</v>
       </c>
       <c r="Q37">
-        <v>825.71831715</v>
+        <v>822.36769764</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0925020288190702</v>
+        <v>0.09307275891986191</v>
       </c>
       <c r="T37">
-        <v>0.6795714240088858</v>
+        <v>0.6878762423888827</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.677940886221366</v>
+        <v>4.547998083826327</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07325016570871162</v>
+        <v>0.07307051268502761</v>
       </c>
       <c r="C38">
-        <v>6460.541626694845</v>
+        <v>6404.768733657316</v>
       </c>
       <c r="D38">
-        <v>9309.077626694845</v>
+        <v>9341.455733657316</v>
       </c>
       <c r="E38">
-        <v>1186.736</v>
+        <v>1274.887</v>
       </c>
       <c r="F38">
-        <v>3173.436</v>
+        <v>3261.587</v>
       </c>
       <c r="G38">
         <v>324.9</v>
@@ -4409,28 +4409,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M38">
-        <v>172.3175748</v>
+        <v>177.1041741</v>
       </c>
       <c r="N38">
-        <v>611.3824251999999</v>
+        <v>606.5958258999999</v>
       </c>
       <c r="O38">
-        <v>183.41472756</v>
+        <v>181.97874777</v>
       </c>
       <c r="P38">
-        <v>427.96769764</v>
+        <v>424.61707813</v>
       </c>
       <c r="Q38">
-        <v>822.36769764</v>
+        <v>819.01707813</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09307275891986191</v>
+        <v>0.09366160743655176</v>
       </c>
       <c r="T38">
-        <v>0.6878762423888827</v>
+        <v>0.6964447057968158</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.547998083826327</v>
+        <v>4.425079216695886</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07307051268502761</v>
+        <v>0.07289085966134359</v>
       </c>
       <c r="C39">
-        <v>6404.768733657316</v>
+        <v>6349.221856738611</v>
       </c>
       <c r="D39">
-        <v>9341.455733657316</v>
+        <v>9374.059856738611</v>
       </c>
       <c r="E39">
-        <v>1274.887</v>
+        <v>1363.038</v>
       </c>
       <c r="F39">
-        <v>3261.587</v>
+        <v>3349.738</v>
       </c>
       <c r="G39">
         <v>324.9</v>
@@ -4491,28 +4491,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M39">
-        <v>177.1041741</v>
+        <v>181.8907734</v>
       </c>
       <c r="N39">
-        <v>606.5958258999999</v>
+        <v>601.8092265999999</v>
       </c>
       <c r="O39">
-        <v>181.97874777</v>
+        <v>180.54276798</v>
       </c>
       <c r="P39">
-        <v>424.61707813</v>
+        <v>421.2664586199999</v>
       </c>
       <c r="Q39">
-        <v>819.01707813</v>
+        <v>815.66645862</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09366160743655176</v>
+        <v>0.09426945106668323</v>
       </c>
       <c r="T39">
-        <v>0.6964447057968158</v>
+        <v>0.7052895712501663</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.425079216695886</v>
+        <v>4.308629763624941</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07289085966134359</v>
+        <v>0.07298420663765959</v>
       </c>
       <c r="C40">
-        <v>6349.221856738611</v>
+        <v>6244.101533628323</v>
       </c>
       <c r="D40">
-        <v>9374.059856738611</v>
+        <v>9357.090533628323</v>
       </c>
       <c r="E40">
-        <v>1363.038</v>
+        <v>1451.189</v>
       </c>
       <c r="F40">
-        <v>3349.738</v>
+        <v>3437.889</v>
       </c>
       <c r="G40">
         <v>324.9</v>
@@ -4573,45 +4573,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M40">
-        <v>181.8907734</v>
+        <v>190.1152617</v>
       </c>
       <c r="N40">
-        <v>601.8092265999999</v>
+        <v>593.5847382999999</v>
       </c>
       <c r="O40">
-        <v>180.54276798</v>
+        <v>178.07542149</v>
       </c>
       <c r="P40">
-        <v>421.2664586199999</v>
+        <v>415.50931681</v>
       </c>
       <c r="Q40">
-        <v>815.66645862</v>
+        <v>809.90931681</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09426945106668323</v>
+        <v>0.09489722399616327</v>
       </c>
       <c r="T40">
-        <v>0.7052895712501663</v>
+        <v>0.7144244322921512</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.308629763624941</v>
+        <v>4.122236126611817</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07298420663765959</v>
+        <v>0.07281155361397559</v>
       </c>
       <c r="C41">
-        <v>6244.101533628323</v>
+        <v>6187.385145632246</v>
       </c>
       <c r="D41">
-        <v>9357.090533628323</v>
+        <v>9388.525145632248</v>
       </c>
       <c r="E41">
-        <v>1451.189</v>
+        <v>1539.34</v>
       </c>
       <c r="F41">
-        <v>3437.889</v>
+        <v>3526.04</v>
       </c>
       <c r="G41">
         <v>324.9</v>
@@ -4655,28 +4655,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M41">
-        <v>190.1152617</v>
+        <v>194.990012</v>
       </c>
       <c r="N41">
-        <v>593.5847382999999</v>
+        <v>588.7099879999998</v>
       </c>
       <c r="O41">
-        <v>178.07542149</v>
+        <v>176.6129964</v>
       </c>
       <c r="P41">
-        <v>415.50931681</v>
+        <v>412.0969915999999</v>
       </c>
       <c r="Q41">
-        <v>809.90931681</v>
+        <v>806.4969915999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09489722399616327</v>
+        <v>0.09554592268995932</v>
       </c>
       <c r="T41">
-        <v>0.7144244322921512</v>
+        <v>0.7238637887022025</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.122236126611817</v>
+        <v>4.01918022344652</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07281155361397559</v>
+        <v>0.07263890059029157</v>
       </c>
       <c r="C42">
-        <v>6187.385145632246</v>
+        <v>6130.880675133483</v>
       </c>
       <c r="D42">
-        <v>9388.525145632248</v>
+        <v>9420.171675133484</v>
       </c>
       <c r="E42">
-        <v>1539.34</v>
+        <v>1627.491</v>
       </c>
       <c r="F42">
-        <v>3526.04</v>
+        <v>3614.191</v>
       </c>
       <c r="G42">
         <v>324.9</v>
@@ -4737,28 +4737,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M42">
-        <v>194.990012</v>
+        <v>199.8647623</v>
       </c>
       <c r="N42">
-        <v>588.7099879999998</v>
+        <v>583.8352376999999</v>
       </c>
       <c r="O42">
-        <v>176.6129964</v>
+        <v>175.1505713099999</v>
       </c>
       <c r="P42">
-        <v>412.0969915999999</v>
+        <v>408.68466639</v>
       </c>
       <c r="Q42">
-        <v>806.4969915999999</v>
+        <v>803.0846663899999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09554592268995932</v>
+        <v>0.09621661116998573</v>
       </c>
       <c r="T42">
-        <v>0.7238637887022025</v>
+        <v>0.7336231232956449</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.01918022344652</v>
+        <v>3.921151437508801</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07263890059029157</v>
+        <v>0.07246624756660758</v>
       </c>
       <c r="C43">
-        <v>6130.880675133483</v>
+        <v>6074.590272353356</v>
       </c>
       <c r="D43">
-        <v>9420.171675133484</v>
+        <v>9452.032272353357</v>
       </c>
       <c r="E43">
-        <v>1627.491</v>
+        <v>1715.642</v>
       </c>
       <c r="F43">
-        <v>3614.191</v>
+        <v>3702.342000000001</v>
       </c>
       <c r="G43">
         <v>324.9</v>
@@ -4819,28 +4819,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M43">
-        <v>199.8647623</v>
+        <v>204.7395126</v>
       </c>
       <c r="N43">
-        <v>583.8352376999999</v>
+        <v>578.9604873999999</v>
       </c>
       <c r="O43">
-        <v>175.1505713099999</v>
+        <v>173.68814622</v>
       </c>
       <c r="P43">
-        <v>408.68466639</v>
+        <v>405.27234118</v>
       </c>
       <c r="Q43">
-        <v>803.0846663899999</v>
+        <v>799.6723411799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09621661116998573</v>
+        <v>0.09691042683897858</v>
       </c>
       <c r="T43">
-        <v>0.7336231232956449</v>
+        <v>0.7437189866681718</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.921151437508801</v>
+        <v>3.827790688996687</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07246624756660758</v>
+        <v>0.07229359454292357</v>
       </c>
       <c r="C44">
-        <v>6074.590272353356</v>
+        <v>6018.516116701556</v>
       </c>
       <c r="D44">
-        <v>9452.032272353357</v>
+        <v>9484.109116701557</v>
       </c>
       <c r="E44">
-        <v>1715.642</v>
+        <v>1803.793</v>
       </c>
       <c r="F44">
-        <v>3702.342</v>
+        <v>3790.493</v>
       </c>
       <c r="G44">
         <v>324.9</v>
@@ -4901,28 +4901,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M44">
-        <v>204.7395126</v>
+        <v>209.6142629</v>
       </c>
       <c r="N44">
-        <v>578.9604873999999</v>
+        <v>574.0857371</v>
       </c>
       <c r="O44">
-        <v>173.68814622</v>
+        <v>172.22572113</v>
       </c>
       <c r="P44">
-        <v>405.27234118</v>
+        <v>401.8600159699999</v>
       </c>
       <c r="Q44">
-        <v>799.6723411799999</v>
+        <v>796.2600159699999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09691042683897858</v>
+        <v>0.09762858691740976</v>
       </c>
       <c r="T44">
-        <v>0.7437189866681717</v>
+        <v>0.7541690908607873</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.827790688996687</v>
+        <v>3.738772300880485</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07229359454292357</v>
+        <v>0.07212094151923956</v>
       </c>
       <c r="C45">
-        <v>6018.516116701556</v>
+        <v>5962.660417273079</v>
       </c>
       <c r="D45">
-        <v>9484.109116701557</v>
+        <v>9516.404417273079</v>
       </c>
       <c r="E45">
-        <v>1803.793</v>
+        <v>1891.944</v>
       </c>
       <c r="F45">
-        <v>3790.493</v>
+        <v>3878.644</v>
       </c>
       <c r="G45">
         <v>324.9</v>
@@ -4983,28 +4983,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M45">
-        <v>209.6142629</v>
+        <v>214.4890132</v>
       </c>
       <c r="N45">
-        <v>574.0857371</v>
+        <v>569.2109867999999</v>
       </c>
       <c r="O45">
-        <v>172.22572113</v>
+        <v>170.76329604</v>
       </c>
       <c r="P45">
-        <v>401.8600159699999</v>
+        <v>398.4476907599999</v>
       </c>
       <c r="Q45">
-        <v>796.2600159699999</v>
+        <v>792.8476907599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09762858691740976</v>
+        <v>0.09837239557007063</v>
       </c>
       <c r="T45">
-        <v>0.7541690908607873</v>
+        <v>0.764992413060282</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.738772300880485</v>
+        <v>3.653800203133201</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07212094151923956</v>
+        <v>0.07194828849555555</v>
       </c>
       <c r="C46">
-        <v>5962.660417273079</v>
+        <v>5907.025413355388</v>
       </c>
       <c r="D46">
-        <v>9516.404417273079</v>
+        <v>9548.920413355389</v>
       </c>
       <c r="E46">
-        <v>1891.944</v>
+        <v>1980.095</v>
       </c>
       <c r="F46">
-        <v>3878.644</v>
+        <v>3966.795</v>
       </c>
       <c r="G46">
         <v>324.9</v>
@@ -5065,28 +5065,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M46">
-        <v>214.4890132</v>
+        <v>219.3637635</v>
       </c>
       <c r="N46">
-        <v>569.2109867999999</v>
+        <v>564.3362364999999</v>
       </c>
       <c r="O46">
-        <v>170.76329604</v>
+        <v>169.30087095</v>
       </c>
       <c r="P46">
-        <v>398.4476907599999</v>
+        <v>395.0353655499999</v>
       </c>
       <c r="Q46">
-        <v>792.8476907599999</v>
+        <v>789.4353655499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09837239557007063</v>
+        <v>0.099143251810101</v>
       </c>
       <c r="T46">
-        <v>0.764992413060282</v>
+        <v>0.7762093106124855</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.653800203133201</v>
+        <v>3.572604643063575</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07194828849555555</v>
+        <v>0.07177563547187155</v>
       </c>
       <c r="C47">
-        <v>5907.025413355388</v>
+        <v>5851.613374945993</v>
       </c>
       <c r="D47">
-        <v>9548.920413355389</v>
+        <v>9581.659374945993</v>
       </c>
       <c r="E47">
-        <v>1980.095</v>
+        <v>2068.246</v>
       </c>
       <c r="F47">
-        <v>3966.795</v>
+        <v>4054.946</v>
       </c>
       <c r="G47">
         <v>324.9</v>
@@ -5147,28 +5147,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M47">
-        <v>219.3637635</v>
+        <v>224.2385138</v>
       </c>
       <c r="N47">
-        <v>564.3362364999999</v>
+        <v>559.4614861999999</v>
       </c>
       <c r="O47">
-        <v>169.30087095</v>
+        <v>167.83844586</v>
       </c>
       <c r="P47">
-        <v>395.0353655499999</v>
+        <v>391.6230403399999</v>
       </c>
       <c r="Q47">
-        <v>789.4353655499999</v>
+        <v>786.0230403399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.099143251810101</v>
+        <v>0.0999426582812436</v>
       </c>
       <c r="T47">
-        <v>0.7762093106124855</v>
+        <v>0.7878416488147707</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.572604643063575</v>
+        <v>3.494939324736105</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07177563547187155</v>
+        <v>0.07160298244818752</v>
       </c>
       <c r="C48">
-        <v>5851.613374945993</v>
+        <v>5796.426603280716</v>
       </c>
       <c r="D48">
-        <v>9581.659374945993</v>
+        <v>9614.623603280717</v>
       </c>
       <c r="E48">
-        <v>2068.246</v>
+        <v>2156.397</v>
       </c>
       <c r="F48">
-        <v>4054.946</v>
+        <v>4143.097000000001</v>
       </c>
       <c r="G48">
         <v>324.9</v>
@@ -5229,28 +5229,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M48">
-        <v>224.2385138</v>
+        <v>229.1132641</v>
       </c>
       <c r="N48">
-        <v>559.4614861999999</v>
+        <v>554.5867358999999</v>
       </c>
       <c r="O48">
-        <v>167.83844586</v>
+        <v>166.37602077</v>
       </c>
       <c r="P48">
-        <v>391.6230403399999</v>
+        <v>388.2107151299999</v>
       </c>
       <c r="Q48">
-        <v>786.0230403399999</v>
+        <v>782.6107151299999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0999426582812436</v>
+        <v>0.1007722310343161</v>
       </c>
       <c r="T48">
-        <v>0.7878416488147707</v>
+        <v>0.7999129431756327</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.494939324736105</v>
+        <v>3.420578913571507</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07160298244818752</v>
+        <v>0.07143032942450353</v>
       </c>
       <c r="C49">
-        <v>5796.426603280716</v>
+        <v>5741.467431372893</v>
       </c>
       <c r="D49">
-        <v>9614.623603280717</v>
+        <v>9647.815431372894</v>
       </c>
       <c r="E49">
-        <v>2156.397</v>
+        <v>2244.548</v>
       </c>
       <c r="F49">
-        <v>4143.097000000001</v>
+        <v>4231.248000000001</v>
       </c>
       <c r="G49">
         <v>324.9</v>
@@ -5311,28 +5311,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M49">
-        <v>229.1132641</v>
+        <v>233.9880144</v>
       </c>
       <c r="N49">
-        <v>554.5867358999999</v>
+        <v>549.7119855999999</v>
       </c>
       <c r="O49">
-        <v>166.37602077</v>
+        <v>164.91359568</v>
       </c>
       <c r="P49">
-        <v>388.2107151299999</v>
+        <v>384.79838992</v>
       </c>
       <c r="Q49">
-        <v>782.6107151299999</v>
+        <v>779.19838992</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1007722310343161</v>
+        <v>0.1016337104317376</v>
       </c>
       <c r="T49">
-        <v>0.7999129431756327</v>
+        <v>0.8124485180888354</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.420578913571507</v>
+        <v>3.349316852872101</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07143032942450353</v>
+        <v>0.07125767640081951</v>
       </c>
       <c r="C50">
-        <v>5741.467431372894</v>
+        <v>5686.73822456381</v>
       </c>
       <c r="D50">
-        <v>9647.815431372894</v>
+        <v>9681.237224563811</v>
       </c>
       <c r="E50">
-        <v>2244.547999999999</v>
+        <v>2332.699</v>
       </c>
       <c r="F50">
-        <v>4231.248</v>
+        <v>4319.399</v>
       </c>
       <c r="G50">
         <v>324.9</v>
@@ -5393,28 +5393,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M50">
-        <v>233.9880144</v>
+        <v>238.8627647</v>
       </c>
       <c r="N50">
-        <v>549.7119855999999</v>
+        <v>544.8372353</v>
       </c>
       <c r="O50">
-        <v>164.91359568</v>
+        <v>163.45117059</v>
       </c>
       <c r="P50">
-        <v>384.79838992</v>
+        <v>381.38606471</v>
       </c>
       <c r="Q50">
-        <v>779.19838992</v>
+        <v>775.78606471</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1016337104317376</v>
+        <v>0.1025289733349402</v>
       </c>
       <c r="T50">
-        <v>0.8124485180888354</v>
+        <v>0.825475684175105</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.349316852872101</v>
+        <v>3.280963447711446</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07125767640081951</v>
+        <v>0.07108502337713551</v>
       </c>
       <c r="C51">
-        <v>5686.73822456381</v>
+        <v>5632.241381084564</v>
       </c>
       <c r="D51">
-        <v>9681.237224563811</v>
+        <v>9714.891381084564</v>
       </c>
       <c r="E51">
-        <v>2332.699</v>
+        <v>2420.85</v>
       </c>
       <c r="F51">
-        <v>4319.399</v>
+        <v>4407.55</v>
       </c>
       <c r="G51">
         <v>324.9</v>
@@ -5475,28 +5475,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M51">
-        <v>238.8627647</v>
+        <v>243.737515</v>
       </c>
       <c r="N51">
-        <v>544.8372353</v>
+        <v>539.9624849999999</v>
       </c>
       <c r="O51">
-        <v>163.45117059</v>
+        <v>161.9887455</v>
       </c>
       <c r="P51">
-        <v>381.38606471</v>
+        <v>377.9737395</v>
       </c>
       <c r="Q51">
-        <v>775.78606471</v>
+        <v>772.3737394999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1025289733349402</v>
+        <v>0.103460046754271</v>
       </c>
       <c r="T51">
-        <v>0.825475684175105</v>
+        <v>0.8390239369048255</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.280963447711446</v>
+        <v>3.215344178757217</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07108502337713551</v>
+        <v>0.07091237035345151</v>
       </c>
       <c r="C52">
-        <v>5632.241381084564</v>
+        <v>5577.979332629763</v>
       </c>
       <c r="D52">
-        <v>9714.891381084564</v>
+        <v>9748.780332629764</v>
       </c>
       <c r="E52">
-        <v>2420.85</v>
+        <v>2509.001</v>
       </c>
       <c r="F52">
-        <v>4407.55</v>
+        <v>4495.701</v>
       </c>
       <c r="G52">
         <v>324.9</v>
@@ -5557,28 +5557,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M52">
-        <v>243.737515</v>
+        <v>248.6122653</v>
       </c>
       <c r="N52">
-        <v>539.9624849999999</v>
+        <v>535.0877346999999</v>
       </c>
       <c r="O52">
-        <v>161.9887455</v>
+        <v>160.52632041</v>
       </c>
       <c r="P52">
-        <v>377.9737395</v>
+        <v>374.56141429</v>
       </c>
       <c r="Q52">
-        <v>772.3737394999999</v>
+        <v>768.96141429</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.103460046754271</v>
+        <v>0.1044291231703092</v>
       </c>
       <c r="T52">
-        <v>0.8390239369048255</v>
+        <v>0.8531251795418814</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.215344178757217</v>
+        <v>3.15229821446786</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07091237035345151</v>
+        <v>0.0707397173297675</v>
       </c>
       <c r="C53">
-        <v>5577.979332629763</v>
+        <v>5523.954544943188</v>
       </c>
       <c r="D53">
-        <v>9748.780332629764</v>
+        <v>9782.906544943189</v>
       </c>
       <c r="E53">
-        <v>2509.001</v>
+        <v>2597.152</v>
       </c>
       <c r="F53">
-        <v>4495.701</v>
+        <v>4583.852000000001</v>
       </c>
       <c r="G53">
         <v>324.9</v>
@@ -5639,28 +5639,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M53">
-        <v>248.6122653</v>
+        <v>253.4870156000001</v>
       </c>
       <c r="N53">
-        <v>535.0877346999999</v>
+        <v>530.2129843999999</v>
       </c>
       <c r="O53">
-        <v>160.52632041</v>
+        <v>159.0638953199999</v>
       </c>
       <c r="P53">
-        <v>374.56141429</v>
+        <v>371.14908908</v>
       </c>
       <c r="Q53">
-        <v>768.96141429</v>
+        <v>765.5490890799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1044291231703092</v>
+        <v>0.105438577770349</v>
       </c>
       <c r="T53">
-        <v>0.8531251795418814</v>
+        <v>0.8678139739554812</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.15229821446786</v>
+        <v>3.091677094958862</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0707397173297675</v>
+        <v>0.07056706430608349</v>
       </c>
       <c r="C54">
-        <v>5523.954544943188</v>
+        <v>5470.169518415876</v>
       </c>
       <c r="D54">
-        <v>9782.906544943189</v>
+        <v>9817.272518415877</v>
       </c>
       <c r="E54">
-        <v>2597.152</v>
+        <v>2685.303</v>
       </c>
       <c r="F54">
-        <v>4583.852000000001</v>
+        <v>4672.003000000001</v>
       </c>
       <c r="G54">
         <v>324.9</v>
@@ -5721,28 +5721,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M54">
-        <v>253.4870156000001</v>
+        <v>258.3617659</v>
       </c>
       <c r="N54">
-        <v>530.2129843999999</v>
+        <v>525.3382340999999</v>
       </c>
       <c r="O54">
-        <v>159.0638953199999</v>
+        <v>157.60147023</v>
       </c>
       <c r="P54">
-        <v>371.14908908</v>
+        <v>367.7367638699999</v>
       </c>
       <c r="Q54">
-        <v>765.5490890799999</v>
+        <v>762.1367638699999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.105438577770349</v>
+        <v>0.106490987885284</v>
       </c>
       <c r="T54">
-        <v>0.8678139739554812</v>
+        <v>0.8831278234505109</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.091677094958862</v>
+        <v>3.033343564865299</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07056706430608349</v>
+        <v>0.07133941128239948</v>
       </c>
       <c r="C55">
-        <v>5470.169518415876</v>
+        <v>5230.13235001776</v>
       </c>
       <c r="D55">
-        <v>9817.272518415877</v>
+        <v>9665.386350017761</v>
       </c>
       <c r="E55">
-        <v>2685.303</v>
+        <v>2773.454</v>
       </c>
       <c r="F55">
-        <v>4672.003000000001</v>
+        <v>4760.154</v>
       </c>
       <c r="G55">
         <v>324.9</v>
@@ -5803,45 +5803,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M55">
-        <v>258.3617659</v>
+        <v>275.1369012000001</v>
       </c>
       <c r="N55">
-        <v>525.3382340999999</v>
+        <v>508.5630987999999</v>
       </c>
       <c r="O55">
-        <v>157.60147023</v>
+        <v>152.56892964</v>
       </c>
       <c r="P55">
-        <v>367.7367638699999</v>
+        <v>355.9941691599999</v>
       </c>
       <c r="Q55">
-        <v>762.1367638699999</v>
+        <v>750.3941691599998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.106490987885284</v>
+        <v>0.107589154961738</v>
       </c>
       <c r="T55">
-        <v>0.8831278234505109</v>
+        <v>0.8991074924888027</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.033343564865299</v>
+        <v>2.848400183988115</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07133941128239948</v>
+        <v>0.07118425825871547</v>
       </c>
       <c r="C56">
-        <v>5230.13235001776</v>
+        <v>5172.114619964665</v>
       </c>
       <c r="D56">
-        <v>9665.386350017761</v>
+        <v>9695.519619964665</v>
       </c>
       <c r="E56">
-        <v>2773.454</v>
+        <v>2861.605</v>
       </c>
       <c r="F56">
-        <v>4760.154</v>
+        <v>4848.305</v>
       </c>
       <c r="G56">
         <v>324.9</v>
@@ -5885,28 +5885,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M56">
-        <v>275.1369012000001</v>
+        <v>280.232029</v>
       </c>
       <c r="N56">
-        <v>508.5630987999999</v>
+        <v>503.4679709999999</v>
       </c>
       <c r="O56">
-        <v>152.56892964</v>
+        <v>151.0403913</v>
       </c>
       <c r="P56">
-        <v>355.9941691599999</v>
+        <v>352.4275796999999</v>
       </c>
       <c r="Q56">
-        <v>750.3941691599998</v>
+        <v>746.8275796999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.107589154961738</v>
+        <v>0.1087361294638122</v>
       </c>
       <c r="T56">
-        <v>0.8991074924888027</v>
+        <v>0.9157973690399076</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.848400183988115</v>
+        <v>2.796611089733786</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07118425825871547</v>
+        <v>0.07102910523503146</v>
       </c>
       <c r="C57">
-        <v>5172.114619964665</v>
+        <v>5114.285367359983</v>
       </c>
       <c r="D57">
-        <v>9695.519619964665</v>
+        <v>9725.841367359984</v>
       </c>
       <c r="E57">
-        <v>2861.605</v>
+        <v>2949.756000000001</v>
       </c>
       <c r="F57">
-        <v>4848.305</v>
+        <v>4936.456000000001</v>
       </c>
       <c r="G57">
         <v>324.9</v>
@@ -5967,28 +5967,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M57">
-        <v>280.232029</v>
+        <v>285.3271568000001</v>
       </c>
       <c r="N57">
-        <v>503.4679709999999</v>
+        <v>498.3728431999999</v>
       </c>
       <c r="O57">
-        <v>151.0403913</v>
+        <v>149.5118529599999</v>
       </c>
       <c r="P57">
-        <v>352.4275796999999</v>
+        <v>348.8609902399999</v>
       </c>
       <c r="Q57">
-        <v>746.8275796999999</v>
+        <v>743.26099024</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1087361294638122</v>
+        <v>0.1099352391705261</v>
       </c>
       <c r="T57">
-        <v>0.9157973690399076</v>
+        <v>0.9332458763433353</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.796611089733786</v>
+        <v>2.746671605988539</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07102910523503146</v>
+        <v>0.07087395221134746</v>
       </c>
       <c r="C58">
-        <v>5114.285367359983</v>
+        <v>5056.646366083257</v>
       </c>
       <c r="D58">
-        <v>9725.841367359984</v>
+        <v>9756.353366083258</v>
       </c>
       <c r="E58">
-        <v>2949.756000000001</v>
+        <v>3037.907000000001</v>
       </c>
       <c r="F58">
-        <v>4936.456000000001</v>
+        <v>5024.607000000001</v>
       </c>
       <c r="G58">
         <v>324.9</v>
@@ -6049,28 +6049,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M58">
-        <v>285.3271568000001</v>
+        <v>290.4222846000001</v>
       </c>
       <c r="N58">
-        <v>498.3728431999999</v>
+        <v>493.2777153999999</v>
       </c>
       <c r="O58">
-        <v>149.5118529599999</v>
+        <v>147.98331462</v>
       </c>
       <c r="P58">
-        <v>348.8609902399999</v>
+        <v>345.2944007799999</v>
       </c>
       <c r="Q58">
-        <v>743.26099024</v>
+        <v>739.6944007799999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1099352391705261</v>
+        <v>0.1111901214217383</v>
       </c>
       <c r="T58">
-        <v>0.9332458763433353</v>
+        <v>0.9515059421259923</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.746671605988539</v>
+        <v>2.698484384830846</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07087395221134746</v>
+        <v>0.07071879918766345</v>
       </c>
       <c r="C59">
-        <v>5056.646366083257</v>
+        <v>4999.199412344205</v>
       </c>
       <c r="D59">
-        <v>9756.353366083258</v>
+        <v>9787.057412344206</v>
       </c>
       <c r="E59">
-        <v>3037.907000000001</v>
+        <v>3126.058</v>
       </c>
       <c r="F59">
-        <v>5024.607000000001</v>
+        <v>5112.758000000001</v>
       </c>
       <c r="G59">
         <v>324.9</v>
@@ -6131,28 +6131,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M59">
-        <v>290.4222846000001</v>
+        <v>295.5174124000001</v>
       </c>
       <c r="N59">
-        <v>493.2777153999999</v>
+        <v>488.1825875999999</v>
       </c>
       <c r="O59">
-        <v>147.98331462</v>
+        <v>146.4547762799999</v>
       </c>
       <c r="P59">
-        <v>345.2944007799999</v>
+        <v>341.7278113199999</v>
       </c>
       <c r="Q59">
-        <v>739.6944007799999</v>
+        <v>736.1278113199999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1111901214217383</v>
+        <v>0.1125047599706273</v>
       </c>
       <c r="T59">
-        <v>0.9515059421259923</v>
+        <v>0.9706355348506805</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.698484384830846</v>
+        <v>2.651958791988934</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07071879918766345</v>
+        <v>0.07056364616397943</v>
       </c>
       <c r="C60">
-        <v>4999.199412344205</v>
+        <v>4941.946325035209</v>
       </c>
       <c r="D60">
-        <v>9787.057412344206</v>
+        <v>9817.955325035209</v>
       </c>
       <c r="E60">
-        <v>3126.058</v>
+        <v>3214.208999999999</v>
       </c>
       <c r="F60">
-        <v>5112.758</v>
+        <v>5200.909</v>
       </c>
       <c r="G60">
         <v>324.9</v>
@@ -6213,28 +6213,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M60">
-        <v>295.5174124</v>
+        <v>300.6125402</v>
       </c>
       <c r="N60">
-        <v>488.1825875999999</v>
+        <v>483.0874597999999</v>
       </c>
       <c r="O60">
-        <v>146.45477628</v>
+        <v>144.92623794</v>
       </c>
       <c r="P60">
-        <v>341.7278113199999</v>
+        <v>338.16122186</v>
       </c>
       <c r="Q60">
-        <v>736.1278113199999</v>
+        <v>732.5612218599999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1125047599706273</v>
+        <v>0.1138835272292181</v>
       </c>
       <c r="T60">
-        <v>0.9706355348506803</v>
+        <v>0.9906982784399874</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.651958791988935</v>
+        <v>2.607010337887428</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07056364616397943</v>
+        <v>0.07040849314029544</v>
       </c>
       <c r="C61">
-        <v>4941.946325035209</v>
+        <v>4884.888946090486</v>
       </c>
       <c r="D61">
-        <v>9817.955325035209</v>
+        <v>9849.048946090486</v>
       </c>
       <c r="E61">
-        <v>3214.208999999999</v>
+        <v>3302.36</v>
       </c>
       <c r="F61">
-        <v>5200.909</v>
+        <v>5289.06</v>
       </c>
       <c r="G61">
         <v>324.9</v>
@@ -6295,28 +6295,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M61">
-        <v>300.6125402</v>
+        <v>305.7076680000001</v>
       </c>
       <c r="N61">
-        <v>483.0874597999999</v>
+        <v>477.9923319999999</v>
       </c>
       <c r="O61">
-        <v>144.92623794</v>
+        <v>143.3976996</v>
       </c>
       <c r="P61">
-        <v>338.16122186</v>
+        <v>334.5946323999999</v>
       </c>
       <c r="Q61">
-        <v>732.5612218599999</v>
+        <v>728.9946323999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1138835272292181</v>
+        <v>0.1153312328507386</v>
       </c>
       <c r="T61">
-        <v>0.9906982784399874</v>
+        <v>1.01176415920876</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.607010337887428</v>
+        <v>2.563560165589303</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07040849314029544</v>
+        <v>0.07025334011661143</v>
       </c>
       <c r="C62">
-        <v>4884.888946090486</v>
+        <v>4828.029140852147</v>
       </c>
       <c r="D62">
-        <v>9849.048946090486</v>
+        <v>9880.340140852148</v>
       </c>
       <c r="E62">
-        <v>3302.36</v>
+        <v>3390.511</v>
       </c>
       <c r="F62">
-        <v>5289.06</v>
+        <v>5377.211</v>
       </c>
       <c r="G62">
         <v>324.9</v>
@@ -6377,28 +6377,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M62">
-        <v>305.7076680000001</v>
+        <v>310.8027958</v>
       </c>
       <c r="N62">
-        <v>477.9923319999999</v>
+        <v>472.8972041999999</v>
       </c>
       <c r="O62">
-        <v>143.3976996</v>
+        <v>141.86916126</v>
       </c>
       <c r="P62">
-        <v>334.5946323999999</v>
+        <v>331.02804294</v>
       </c>
       <c r="Q62">
-        <v>728.9946323999999</v>
+        <v>725.42804294</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1153312328507386</v>
+        <v>0.1168531797861831</v>
       </c>
       <c r="T62">
-        <v>1.01176415920876</v>
+        <v>1.033910341555418</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.563560165589303</v>
+        <v>2.521534589104233</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07025334011661143</v>
+        <v>0.07161718709292741</v>
       </c>
       <c r="C63">
-        <v>4828.029140852147</v>
+        <v>4471.440984119204</v>
       </c>
       <c r="D63">
-        <v>9880.340140852148</v>
+        <v>9611.902984119204</v>
       </c>
       <c r="E63">
-        <v>3390.511</v>
+        <v>3478.662</v>
       </c>
       <c r="F63">
-        <v>5377.211</v>
+        <v>5465.362</v>
       </c>
       <c r="G63">
         <v>324.9</v>
@@ -6459,45 +6459,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M63">
-        <v>310.8027958</v>
+        <v>335.0266906</v>
       </c>
       <c r="N63">
-        <v>472.8972041999999</v>
+        <v>448.6733093999999</v>
       </c>
       <c r="O63">
-        <v>141.86916126</v>
+        <v>134.60199282</v>
       </c>
       <c r="P63">
-        <v>331.02804294</v>
+        <v>314.07131658</v>
       </c>
       <c r="Q63">
-        <v>725.42804294</v>
+        <v>708.4713165799999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1168531797861831</v>
+        <v>0.1184552291919143</v>
       </c>
       <c r="T63">
-        <v>1.033910341555418</v>
+        <v>1.057222112446637</v>
       </c>
       <c r="U63">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V63">
         <v>0.3</v>
       </c>
       <c r="W63">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.521534589104233</v>
+        <v>2.339216611657029</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07161718709292741</v>
+        <v>0.07148653406924341</v>
       </c>
       <c r="C64">
-        <v>4471.440984119204</v>
+        <v>4408.372191002795</v>
       </c>
       <c r="D64">
-        <v>9611.902984119204</v>
+        <v>9636.985191002796</v>
       </c>
       <c r="E64">
-        <v>3478.662</v>
+        <v>3566.813</v>
       </c>
       <c r="F64">
-        <v>5465.362</v>
+        <v>5553.513</v>
       </c>
       <c r="G64">
         <v>324.9</v>
@@ -6541,28 +6541,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M64">
-        <v>335.0266906</v>
+        <v>340.4303469</v>
       </c>
       <c r="N64">
-        <v>448.6733093999999</v>
+        <v>443.2696530999999</v>
       </c>
       <c r="O64">
-        <v>134.60199282</v>
+        <v>132.98089593</v>
       </c>
       <c r="P64">
-        <v>314.07131658</v>
+        <v>310.2887571699999</v>
       </c>
       <c r="Q64">
-        <v>708.4713165799999</v>
+        <v>704.6887571699999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1184552291919143</v>
+        <v>0.12014387586282</v>
       </c>
       <c r="T64">
-        <v>1.057222112446637</v>
+        <v>1.081793979061707</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.339216611657029</v>
+        <v>2.302086189249775</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07148653406924341</v>
+        <v>0.0713558810455594</v>
       </c>
       <c r="C65">
-        <v>4408.372191002795</v>
+        <v>4345.434644128864</v>
       </c>
       <c r="D65">
-        <v>9636.985191002796</v>
+        <v>9662.198644128865</v>
       </c>
       <c r="E65">
-        <v>3566.813</v>
+        <v>3654.964</v>
       </c>
       <c r="F65">
-        <v>5553.513</v>
+        <v>5641.664000000001</v>
       </c>
       <c r="G65">
         <v>324.9</v>
@@ -6623,28 +6623,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M65">
-        <v>340.4303469</v>
+        <v>345.8340032</v>
       </c>
       <c r="N65">
-        <v>443.2696530999999</v>
+        <v>437.8659967999999</v>
       </c>
       <c r="O65">
-        <v>132.98089593</v>
+        <v>131.35979904</v>
       </c>
       <c r="P65">
-        <v>310.2887571699999</v>
+        <v>306.50619776</v>
       </c>
       <c r="Q65">
-        <v>704.6887571699999</v>
+        <v>700.9061977599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.12014387586282</v>
+        <v>0.121926336237665</v>
       </c>
       <c r="T65">
-        <v>1.081793979061707</v>
+        <v>1.107730949377613</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.302086189249775</v>
+        <v>2.266116092542747</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0713558810455594</v>
+        <v>0.07249922802187539</v>
       </c>
       <c r="C66">
-        <v>4345.434644128864</v>
+        <v>4041.014569058521</v>
       </c>
       <c r="D66">
-        <v>9662.198644128865</v>
+        <v>9445.929569058522</v>
       </c>
       <c r="E66">
-        <v>3654.964</v>
+        <v>3743.115</v>
       </c>
       <c r="F66">
-        <v>5641.664000000001</v>
+        <v>5729.815000000001</v>
       </c>
       <c r="G66">
         <v>324.9</v>
@@ -6705,45 +6705,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M66">
-        <v>345.8340032</v>
+        <v>367.2811415</v>
       </c>
       <c r="N66">
-        <v>437.8659967999999</v>
+        <v>416.4188584999999</v>
       </c>
       <c r="O66">
-        <v>131.35979904</v>
+        <v>124.92565755</v>
       </c>
       <c r="P66">
-        <v>306.50619776</v>
+        <v>291.49320095</v>
       </c>
       <c r="Q66">
-        <v>700.9061977599999</v>
+        <v>685.8932009499999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.121926336237665</v>
+        <v>0.1238106514910726</v>
       </c>
       <c r="T66">
-        <v>1.107730949377613</v>
+        <v>1.135150032282999</v>
       </c>
       <c r="U66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.266116092542747</v>
+        <v>2.13378774853323</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07249922802187539</v>
+        <v>0.07238817499819139</v>
       </c>
       <c r="C67">
-        <v>4041.014569058521</v>
+        <v>3973.444296102733</v>
       </c>
       <c r="D67">
-        <v>9445.929569058522</v>
+        <v>9466.510296102733</v>
       </c>
       <c r="E67">
-        <v>3743.115</v>
+        <v>3831.266</v>
       </c>
       <c r="F67">
-        <v>5729.815000000001</v>
+        <v>5817.966</v>
       </c>
       <c r="G67">
         <v>324.9</v>
@@ -6787,28 +6787,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M67">
-        <v>367.2811415</v>
+        <v>372.9316206</v>
       </c>
       <c r="N67">
-        <v>416.4188584999999</v>
+        <v>410.7683793999999</v>
       </c>
       <c r="O67">
-        <v>124.92565755</v>
+        <v>123.23051382</v>
       </c>
       <c r="P67">
-        <v>291.49320095</v>
+        <v>287.5378655799999</v>
       </c>
       <c r="Q67">
-        <v>685.8932009499999</v>
+        <v>681.9378655799999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1238106514910726</v>
+        <v>0.12580580881821</v>
       </c>
       <c r="T67">
-        <v>1.135150032282999</v>
+        <v>1.164182002418114</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.13378774853323</v>
+        <v>2.101457631131212</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07238817499819139</v>
+        <v>0.07227712197450738</v>
       </c>
       <c r="C68">
-        <v>3973.444296102733</v>
+        <v>3905.963901268755</v>
       </c>
       <c r="D68">
-        <v>9466.510296102733</v>
+        <v>9487.180901268755</v>
       </c>
       <c r="E68">
-        <v>3831.266</v>
+        <v>3919.417</v>
       </c>
       <c r="F68">
-        <v>5817.966</v>
+        <v>5906.117</v>
       </c>
       <c r="G68">
         <v>324.9</v>
@@ -6869,28 +6869,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M68">
-        <v>372.9316206</v>
+        <v>378.5820997</v>
       </c>
       <c r="N68">
-        <v>410.7683793999999</v>
+        <v>405.1179002999999</v>
       </c>
       <c r="O68">
-        <v>123.23051382</v>
+        <v>121.53537009</v>
       </c>
       <c r="P68">
-        <v>287.5378655799999</v>
+        <v>283.58253021</v>
       </c>
       <c r="Q68">
-        <v>681.9378655799999</v>
+        <v>677.9825302099999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.12580580881821</v>
+        <v>0.1279218847712345</v>
       </c>
       <c r="T68">
-        <v>1.164182002418114</v>
+        <v>1.194973485894751</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.101457631131212</v>
+        <v>2.070092591860597</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07227712197450738</v>
+        <v>0.07216606895082338</v>
       </c>
       <c r="C69">
-        <v>3905.963901268755</v>
+        <v>3838.573974605296</v>
       </c>
       <c r="D69">
-        <v>9487.180901268755</v>
+        <v>9507.941974605297</v>
       </c>
       <c r="E69">
-        <v>3919.417</v>
+        <v>4007.568000000001</v>
       </c>
       <c r="F69">
-        <v>5906.117</v>
+        <v>5994.268000000001</v>
       </c>
       <c r="G69">
         <v>324.9</v>
@@ -6951,28 +6951,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M69">
-        <v>378.5820997</v>
+        <v>384.2325788000001</v>
       </c>
       <c r="N69">
-        <v>405.1179002999999</v>
+        <v>399.4674211999998</v>
       </c>
       <c r="O69">
-        <v>121.53537009</v>
+        <v>119.8402263599999</v>
       </c>
       <c r="P69">
-        <v>283.58253021</v>
+        <v>279.6271948399999</v>
       </c>
       <c r="Q69">
-        <v>677.9825302099999</v>
+        <v>674.0271948399999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1279218847712345</v>
+        <v>0.1301702154713231</v>
       </c>
       <c r="T69">
-        <v>1.194973485894751</v>
+        <v>1.227689437088679</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.070092591860597</v>
+        <v>2.039650053745</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07216606895082338</v>
+        <v>0.07205501592713937</v>
       </c>
       <c r="C70">
-        <v>3838.573974605296</v>
+        <v>3771.275111337275</v>
       </c>
       <c r="D70">
-        <v>9507.941974605297</v>
+        <v>9528.794111337276</v>
       </c>
       <c r="E70">
-        <v>4007.568000000001</v>
+        <v>4095.719000000001</v>
       </c>
       <c r="F70">
-        <v>5994.268000000001</v>
+        <v>6082.419000000001</v>
       </c>
       <c r="G70">
         <v>324.9</v>
@@ -7033,28 +7033,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M70">
-        <v>384.2325788000001</v>
+        <v>389.8830579000001</v>
       </c>
       <c r="N70">
-        <v>399.4674211999998</v>
+        <v>393.8169420999998</v>
       </c>
       <c r="O70">
-        <v>119.8402263599999</v>
+        <v>118.1450826299999</v>
       </c>
       <c r="P70">
-        <v>279.6271948399999</v>
+        <v>275.6718594699999</v>
       </c>
       <c r="Q70">
-        <v>674.0271948399999</v>
+        <v>670.0718594699999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1301702154713231</v>
+        <v>0.1325635997649657</v>
       </c>
       <c r="T70">
-        <v>1.227689437088679</v>
+        <v>1.262516094811246</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.039650053745</v>
+        <v>2.01008990803855</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07205501592713937</v>
+        <v>0.07576596290345536</v>
       </c>
       <c r="C71">
-        <v>3771.275111337275</v>
+        <v>3032.483660760053</v>
       </c>
       <c r="D71">
-        <v>9528.794111337276</v>
+        <v>8878.153660760054</v>
       </c>
       <c r="E71">
-        <v>4095.719000000001</v>
+        <v>4183.870000000001</v>
       </c>
       <c r="F71">
-        <v>6082.419000000001</v>
+        <v>6170.570000000001</v>
       </c>
       <c r="G71">
         <v>324.9</v>
@@ -7115,45 +7115,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M71">
-        <v>389.8830579000001</v>
+        <v>443.6639830000001</v>
       </c>
       <c r="N71">
-        <v>393.8169420999998</v>
+        <v>340.0360169999998</v>
       </c>
       <c r="O71">
-        <v>118.1450826299999</v>
+        <v>102.0108051</v>
       </c>
       <c r="P71">
-        <v>275.6718594699999</v>
+        <v>238.0252118999999</v>
       </c>
       <c r="Q71">
-        <v>670.0718594699999</v>
+        <v>632.4252118999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1325635997649657</v>
+        <v>0.1351165430115179</v>
       </c>
       <c r="T71">
-        <v>1.262516094811246</v>
+        <v>1.299664529715318</v>
       </c>
       <c r="U71">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.3</v>
       </c>
       <c r="W71">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.01008990803855</v>
+        <v>1.766426913225453</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07576596290345536</v>
+        <v>0.07764780987977135</v>
       </c>
       <c r="C72">
-        <v>3032.483660760053</v>
+        <v>2647.205788623907</v>
       </c>
       <c r="D72">
-        <v>8878.153660760054</v>
+        <v>8581.026788623909</v>
       </c>
       <c r="E72">
-        <v>4183.870000000001</v>
+        <v>4272.021000000001</v>
       </c>
       <c r="F72">
-        <v>6170.570000000001</v>
+        <v>6258.721000000001</v>
       </c>
       <c r="G72">
         <v>324.9</v>
@@ -7197,45 +7197,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M72">
-        <v>443.6639830000001</v>
+        <v>474.4110518000002</v>
       </c>
       <c r="N72">
-        <v>340.0360169999998</v>
+        <v>309.2889481999998</v>
       </c>
       <c r="O72">
-        <v>102.0108051</v>
+        <v>92.78668445999993</v>
       </c>
       <c r="P72">
-        <v>238.0252118999999</v>
+        <v>216.5022637399998</v>
       </c>
       <c r="Q72">
-        <v>632.4252118999998</v>
+        <v>610.9022637399999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1351165430115179</v>
+        <v>0.1378455513095564</v>
       </c>
       <c r="T72">
-        <v>1.299664529715318</v>
+        <v>1.339374925647257</v>
       </c>
       <c r="U72">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V72">
         <v>0.3</v>
       </c>
       <c r="W72">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.766426913225453</v>
+        <v>1.651942965971181</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07764780987977135</v>
+        <v>0.07761865685608735</v>
       </c>
       <c r="C73">
-        <v>2647.205788623909</v>
+        <v>2563.506049581855</v>
       </c>
       <c r="D73">
-        <v>8581.026788623909</v>
+        <v>8585.478049581856</v>
       </c>
       <c r="E73">
-        <v>4272.020999999999</v>
+        <v>4360.172</v>
       </c>
       <c r="F73">
-        <v>6258.721</v>
+        <v>6346.872</v>
       </c>
       <c r="G73">
         <v>324.9</v>
@@ -7279,28 +7279,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M73">
-        <v>474.4110518</v>
+        <v>481.0928976000001</v>
       </c>
       <c r="N73">
-        <v>309.2889481999999</v>
+        <v>302.6071023999999</v>
       </c>
       <c r="O73">
-        <v>92.78668445999998</v>
+        <v>90.78213071999996</v>
       </c>
       <c r="P73">
-        <v>216.50226374</v>
+        <v>211.8249716799999</v>
       </c>
       <c r="Q73">
-        <v>610.90226374</v>
+        <v>606.22497168</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1378455513095564</v>
+        <v>0.1407694887717405</v>
       </c>
       <c r="T73">
-        <v>1.339374925647257</v>
+        <v>1.381921778431477</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.651942965971182</v>
+        <v>1.628999313666026</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07761865685608735</v>
+        <v>0.07758950383240333</v>
       </c>
       <c r="C74">
-        <v>2563.506049581855</v>
+        <v>2479.810930967632</v>
       </c>
       <c r="D74">
-        <v>8585.478049581856</v>
+        <v>8589.933930967632</v>
       </c>
       <c r="E74">
-        <v>4360.172</v>
+        <v>4448.323</v>
       </c>
       <c r="F74">
-        <v>6346.872</v>
+        <v>6435.023</v>
       </c>
       <c r="G74">
         <v>324.9</v>
@@ -7361,28 +7361,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M74">
-        <v>481.0928976000001</v>
+        <v>487.7747434</v>
       </c>
       <c r="N74">
-        <v>302.6071023999999</v>
+        <v>295.9252565999999</v>
       </c>
       <c r="O74">
-        <v>90.78213071999996</v>
+        <v>88.77757697999996</v>
       </c>
       <c r="P74">
-        <v>211.8249716799999</v>
+        <v>207.1476796199999</v>
       </c>
       <c r="Q74">
-        <v>606.22497168</v>
+        <v>601.5476796199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1407694887717405</v>
+        <v>0.1439100141940864</v>
       </c>
       <c r="T74">
-        <v>1.381921778431477</v>
+        <v>1.427620249940454</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.628999313666026</v>
+        <v>1.606684254574711</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07758950383240333</v>
+        <v>0.07756035080871933</v>
       </c>
       <c r="C75">
-        <v>2479.810930967632</v>
+        <v>2396.120439979007</v>
       </c>
       <c r="D75">
-        <v>8589.933930967632</v>
+        <v>8594.394439979007</v>
       </c>
       <c r="E75">
-        <v>4448.323</v>
+        <v>4536.474</v>
       </c>
       <c r="F75">
-        <v>6435.023</v>
+        <v>6523.174</v>
       </c>
       <c r="G75">
         <v>324.9</v>
@@ -7443,28 +7443,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M75">
-        <v>487.7747434</v>
+        <v>494.4565892000001</v>
       </c>
       <c r="N75">
-        <v>295.9252565999999</v>
+        <v>289.2434107999999</v>
       </c>
       <c r="O75">
-        <v>88.77757697999996</v>
+        <v>86.77302323999996</v>
       </c>
       <c r="P75">
-        <v>207.1476796199999</v>
+        <v>202.4703875599999</v>
       </c>
       <c r="Q75">
-        <v>601.5476796199999</v>
+        <v>596.8703875599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1439100141940864</v>
+        <v>0.1472921184950743</v>
       </c>
       <c r="T75">
-        <v>1.427620249940454</v>
+        <v>1.476833988488584</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.606684254574711</v>
+        <v>1.584972305188566</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07756035080871933</v>
+        <v>0.07753119778503532</v>
       </c>
       <c r="C76">
-        <v>2396.120439979007</v>
+        <v>2312.434583828706</v>
       </c>
       <c r="D76">
-        <v>8594.394439979007</v>
+        <v>8598.859583828707</v>
       </c>
       <c r="E76">
-        <v>4536.474</v>
+        <v>4624.625</v>
       </c>
       <c r="F76">
-        <v>6523.174</v>
+        <v>6611.325000000001</v>
       </c>
       <c r="G76">
         <v>324.9</v>
@@ -7525,28 +7525,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M76">
-        <v>494.4565892000001</v>
+        <v>501.1384350000001</v>
       </c>
       <c r="N76">
-        <v>289.2434107999999</v>
+        <v>282.5615649999999</v>
       </c>
       <c r="O76">
-        <v>86.77302323999996</v>
+        <v>84.76846949999995</v>
       </c>
       <c r="P76">
-        <v>202.4703875599999</v>
+        <v>197.7930954999999</v>
       </c>
       <c r="Q76">
-        <v>596.8703875599999</v>
+        <v>592.1930954999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1472921184950743</v>
+        <v>0.1509447911401413</v>
       </c>
       <c r="T76">
-        <v>1.476833988488584</v>
+        <v>1.529984826120564</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.584972305188566</v>
+        <v>1.563839341119385</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07753119778503532</v>
+        <v>0.07750204476135131</v>
       </c>
       <c r="C77">
-        <v>2312.434583828706</v>
+        <v>2228.753369744463</v>
       </c>
       <c r="D77">
-        <v>8598.859583828707</v>
+        <v>8603.329369744464</v>
       </c>
       <c r="E77">
-        <v>4624.625</v>
+        <v>4712.776</v>
       </c>
       <c r="F77">
-        <v>6611.325000000001</v>
+        <v>6699.476000000001</v>
       </c>
       <c r="G77">
         <v>324.9</v>
@@ -7607,28 +7607,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M77">
-        <v>501.1384350000001</v>
+        <v>507.8202808000001</v>
       </c>
       <c r="N77">
-        <v>282.5615649999999</v>
+        <v>275.8797191999998</v>
       </c>
       <c r="O77">
-        <v>84.76846949999995</v>
+        <v>82.76391575999995</v>
       </c>
       <c r="P77">
-        <v>197.7930954999999</v>
+        <v>193.1158034399999</v>
       </c>
       <c r="Q77">
-        <v>592.1930954999999</v>
+        <v>587.5158034399999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1509447911401413</v>
+        <v>0.1549018531722971</v>
       </c>
       <c r="T77">
-        <v>1.529984826120564</v>
+        <v>1.587564900221876</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.563839341119385</v>
+        <v>1.543262507683604</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07750204476135131</v>
+        <v>0.0774728917376673</v>
       </c>
       <c r="C78">
-        <v>2228.753369744463</v>
+        <v>2145.076804969038</v>
       </c>
       <c r="D78">
-        <v>8603.329369744464</v>
+        <v>8607.803804969039</v>
       </c>
       <c r="E78">
-        <v>4712.776</v>
+        <v>4800.927</v>
       </c>
       <c r="F78">
-        <v>6699.476000000001</v>
+        <v>6787.627</v>
       </c>
       <c r="G78">
         <v>324.9</v>
@@ -7689,28 +7689,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M78">
-        <v>507.8202808000001</v>
+        <v>514.5021266000001</v>
       </c>
       <c r="N78">
-        <v>275.8797191999998</v>
+        <v>269.1978733999998</v>
       </c>
       <c r="O78">
-        <v>82.76391575999995</v>
+        <v>80.75936201999994</v>
       </c>
       <c r="P78">
-        <v>193.1158034399999</v>
+        <v>188.4385113799999</v>
       </c>
       <c r="Q78">
-        <v>587.5158034399999</v>
+        <v>582.8385113799999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1549018531722971</v>
+        <v>0.1592030075550752</v>
       </c>
       <c r="T78">
-        <v>1.587564900221876</v>
+        <v>1.650151937288519</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.543262507683604</v>
+        <v>1.523220137453946</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0774728917376673</v>
+        <v>0.0774437387139833</v>
       </c>
       <c r="C79">
-        <v>2145.076804969038</v>
+        <v>2061.404896760265</v>
       </c>
       <c r="D79">
-        <v>8607.803804969039</v>
+        <v>8612.282896760265</v>
       </c>
       <c r="E79">
-        <v>4800.927</v>
+        <v>4889.078</v>
       </c>
       <c r="F79">
-        <v>6787.627</v>
+        <v>6875.778</v>
       </c>
       <c r="G79">
         <v>324.9</v>
@@ -7771,28 +7771,28 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M79">
-        <v>514.5021266000001</v>
+        <v>521.1839724</v>
       </c>
       <c r="N79">
-        <v>269.1978733999998</v>
+        <v>262.5160275999999</v>
       </c>
       <c r="O79">
-        <v>80.75936201999994</v>
+        <v>78.75480827999998</v>
       </c>
       <c r="P79">
-        <v>188.4385113799999</v>
+        <v>183.76121932</v>
       </c>
       <c r="Q79">
-        <v>582.8385113799999</v>
+        <v>578.1612193199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1592030075550752</v>
+        <v>0.1638951759726514</v>
       </c>
       <c r="T79">
-        <v>1.650151937288519</v>
+        <v>1.718428704997584</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.523220137453946</v>
+        <v>1.503691674153255</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0774437387139833</v>
+        <v>0.08526718569029929</v>
       </c>
       <c r="C80">
-        <v>2061.404896760265</v>
+        <v>917.9866418896272</v>
       </c>
       <c r="D80">
-        <v>8612.282896760265</v>
+        <v>7557.015641889629</v>
       </c>
       <c r="E80">
-        <v>4889.078</v>
+        <v>4977.229000000001</v>
       </c>
       <c r="F80">
-        <v>6875.778</v>
+        <v>6963.929000000001</v>
       </c>
       <c r="G80">
         <v>324.9</v>
@@ -7853,45 +7853,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M80">
-        <v>521.1839724</v>
+        <v>626.7536100000001</v>
       </c>
       <c r="N80">
-        <v>262.5160275999999</v>
+        <v>156.9463899999998</v>
       </c>
       <c r="O80">
-        <v>78.75480827999998</v>
+        <v>47.08391699999995</v>
       </c>
       <c r="P80">
-        <v>183.76121932</v>
+        <v>109.8624729999999</v>
       </c>
       <c r="Q80">
-        <v>578.1612193199999</v>
+        <v>504.2624729999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1638951759726514</v>
+        <v>0.1690342175728538</v>
       </c>
       <c r="T80">
-        <v>1.718428704997584</v>
+        <v>1.793208022012274</v>
       </c>
       <c r="U80">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.3</v>
       </c>
       <c r="W80">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.503691674153255</v>
+        <v>1.250411625072251</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08526718569029929</v>
+        <v>0.1036588415301449</v>
       </c>
       <c r="C81">
-        <v>917.9866418896272</v>
+        <v>-860.156516639111</v>
       </c>
       <c r="D81">
-        <v>7557.015641889629</v>
+        <v>5867.02348336089</v>
       </c>
       <c r="E81">
-        <v>4977.229000000001</v>
+        <v>5065.380000000001</v>
       </c>
       <c r="F81">
-        <v>6963.929000000001</v>
+        <v>7052.080000000001</v>
       </c>
       <c r="G81">
         <v>324.9</v>
@@ -7935,45 +7935,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M81">
-        <v>626.7536100000001</v>
+        <v>836.3766880000002</v>
       </c>
       <c r="N81">
-        <v>156.9463899999998</v>
+        <v>-52.67668800000024</v>
       </c>
       <c r="O81">
-        <v>47.08391699999995</v>
+        <v>-15.80300640000007</v>
       </c>
       <c r="P81">
-        <v>109.8624729999999</v>
+        <v>-36.87368160000017</v>
       </c>
       <c r="Q81">
-        <v>504.2624729999999</v>
+        <v>357.5263183999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1690342175728538</v>
+        <v>0.17725060746468</v>
       </c>
       <c r="T81">
-        <v>1.793208022012274</v>
+        <v>1.912766506304943</v>
       </c>
       <c r="U81">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V81">
-        <v>0.3</v>
+        <v>0.2811053958978827</v>
       </c>
       <c r="W81">
-        <v>0.063</v>
+        <v>0.08526090004651113</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.250411625072251</v>
+        <v>0.9370179863262758</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1036588415301449</v>
+        <v>0.1043868415301449</v>
       </c>
       <c r="C82">
-        <v>-860.156516639111</v>
+        <v>-999.7871271774902</v>
       </c>
       <c r="D82">
-        <v>5867.02348336089</v>
+        <v>5815.543872822511</v>
       </c>
       <c r="E82">
-        <v>5065.380000000001</v>
+        <v>5153.531000000001</v>
       </c>
       <c r="F82">
-        <v>7052.080000000001</v>
+        <v>7140.231000000001</v>
       </c>
       <c r="G82">
         <v>324.9</v>
@@ -8017,37 +8017,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M82">
-        <v>836.3766880000002</v>
+        <v>846.8313966000002</v>
       </c>
       <c r="N82">
-        <v>-52.67668800000024</v>
+        <v>-63.13139660000024</v>
       </c>
       <c r="O82">
-        <v>-15.80300640000007</v>
+        <v>-18.93941898000007</v>
       </c>
       <c r="P82">
-        <v>-36.87368160000017</v>
+        <v>-44.19197762000017</v>
       </c>
       <c r="Q82">
-        <v>357.5263183999998</v>
+        <v>350.2080223799998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.17725060746468</v>
+        <v>0.1841690604891369</v>
       </c>
       <c r="T82">
-        <v>1.912766506304943</v>
+        <v>2.013438427689414</v>
       </c>
       <c r="U82">
         <v>0.1186</v>
       </c>
       <c r="V82">
-        <v>0.2811053958978827</v>
+        <v>0.2776349589114891</v>
       </c>
       <c r="W82">
-        <v>0.08526090004651113</v>
+        <v>0.0856724938730974</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.9370179863262758</v>
+        <v>0.925449863038297</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1043868415301449</v>
+        <v>0.1051148415301449</v>
       </c>
       <c r="C83">
-        <v>-999.7871271774902</v>
+        <v>-1138.522190223829</v>
       </c>
       <c r="D83">
-        <v>5815.543872822511</v>
+        <v>5764.959809776172</v>
       </c>
       <c r="E83">
-        <v>5153.531000000001</v>
+        <v>5241.682000000001</v>
       </c>
       <c r="F83">
-        <v>7140.231000000001</v>
+        <v>7228.382000000001</v>
       </c>
       <c r="G83">
         <v>324.9</v>
@@ -8099,37 +8099,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M83">
-        <v>846.8313966000002</v>
+        <v>857.2861052000002</v>
       </c>
       <c r="N83">
-        <v>-63.13139660000024</v>
+        <v>-73.58610520000025</v>
       </c>
       <c r="O83">
-        <v>-18.93941898000007</v>
+        <v>-22.07583156000007</v>
       </c>
       <c r="P83">
-        <v>-44.19197762000017</v>
+        <v>-51.51027364000018</v>
       </c>
       <c r="Q83">
-        <v>350.2080223799998</v>
+        <v>342.8897263599998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1841690604891369</v>
+        <v>0.1918562305163111</v>
       </c>
       <c r="T83">
-        <v>2.013438427689414</v>
+        <v>2.125296118116604</v>
       </c>
       <c r="U83">
         <v>0.1186</v>
       </c>
       <c r="V83">
-        <v>0.2776349589114891</v>
+        <v>0.2742491667296417</v>
       </c>
       <c r="W83">
-        <v>0.0856724938730974</v>
+        <v>0.08607404882586452</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.925449863038297</v>
+        <v>0.9141638890988055</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1051148415301449</v>
+        <v>0.1058428415301449</v>
       </c>
       <c r="C84">
-        <v>-1138.522190223829</v>
+        <v>-1276.38487289857</v>
       </c>
       <c r="D84">
-        <v>5764.959809776172</v>
+        <v>5715.248127101431</v>
       </c>
       <c r="E84">
-        <v>5241.682000000001</v>
+        <v>5329.833000000001</v>
       </c>
       <c r="F84">
-        <v>7228.382000000001</v>
+        <v>7316.533000000001</v>
       </c>
       <c r="G84">
         <v>324.9</v>
@@ -8181,37 +8181,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M84">
-        <v>857.2861052000002</v>
+        <v>867.7408138000002</v>
       </c>
       <c r="N84">
-        <v>-73.58610520000025</v>
+        <v>-84.04081380000025</v>
       </c>
       <c r="O84">
-        <v>-22.07583156000007</v>
+        <v>-25.21224414000007</v>
       </c>
       <c r="P84">
-        <v>-51.51027364000018</v>
+        <v>-58.82856966000018</v>
       </c>
       <c r="Q84">
-        <v>342.8897263599998</v>
+        <v>335.5714303399998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1918562305163111</v>
+        <v>0.2004477734878589</v>
       </c>
       <c r="T84">
-        <v>2.125296118116604</v>
+        <v>2.250313536829345</v>
       </c>
       <c r="U84">
         <v>0.1186</v>
       </c>
       <c r="V84">
-        <v>0.2742491667296417</v>
+        <v>0.2709449599015737</v>
       </c>
       <c r="W84">
-        <v>0.08607404882586452</v>
+        <v>0.08646592775567337</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9141638890988055</v>
+        <v>0.903149866338579</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1058428415301449</v>
+        <v>0.1065708415301449</v>
       </c>
       <c r="C85">
-        <v>-1276.38487289857</v>
+        <v>-1413.397550066528</v>
       </c>
       <c r="D85">
-        <v>5715.248127101431</v>
+        <v>5666.386449933473</v>
       </c>
       <c r="E85">
-        <v>5329.833000000001</v>
+        <v>5417.984</v>
       </c>
       <c r="F85">
-        <v>7316.533000000001</v>
+        <v>7404.684000000001</v>
       </c>
       <c r="G85">
         <v>324.9</v>
@@ -8263,37 +8263,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M85">
-        <v>867.7408138000002</v>
+        <v>878.1955224000002</v>
       </c>
       <c r="N85">
-        <v>-84.04081380000025</v>
+        <v>-94.49552240000025</v>
       </c>
       <c r="O85">
-        <v>-25.21224414000007</v>
+        <v>-28.34865672000008</v>
       </c>
       <c r="P85">
-        <v>-58.82856966000018</v>
+        <v>-66.14686568000018</v>
       </c>
       <c r="Q85">
-        <v>335.5714303399998</v>
+        <v>328.2531343199998</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2004477734878589</v>
+        <v>0.2101132593308501</v>
       </c>
       <c r="T85">
-        <v>2.250313536829345</v>
+        <v>2.39095813288118</v>
       </c>
       <c r="U85">
         <v>0.1186</v>
       </c>
       <c r="V85">
-        <v>0.2709449599015737</v>
+        <v>0.2677194246646502</v>
       </c>
       <c r="W85">
-        <v>0.08646592775567337</v>
+        <v>0.0868484762347725</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.903149866338579</v>
+        <v>0.8923980822155007</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1065708415301449</v>
+        <v>0.1072988415301449</v>
       </c>
       <c r="C86">
-        <v>-1413.397550066527</v>
+        <v>-1549.581837916193</v>
       </c>
       <c r="D86">
-        <v>5666.386449933473</v>
+        <v>5618.353162083808</v>
       </c>
       <c r="E86">
-        <v>5417.984</v>
+        <v>5506.135</v>
       </c>
       <c r="F86">
-        <v>7404.684</v>
+        <v>7492.835</v>
       </c>
       <c r="G86">
         <v>324.9</v>
@@ -8345,37 +8345,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M86">
-        <v>878.1955224000001</v>
+        <v>888.6502310000001</v>
       </c>
       <c r="N86">
-        <v>-94.49552240000014</v>
+        <v>-104.9502310000001</v>
       </c>
       <c r="O86">
-        <v>-28.34865672000004</v>
+        <v>-31.48506930000004</v>
       </c>
       <c r="P86">
-        <v>-66.1468656800001</v>
+        <v>-73.4651617000001</v>
       </c>
       <c r="Q86">
-        <v>328.2531343199998</v>
+        <v>320.9348382999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.21011325933085</v>
+        <v>0.2210674766195733</v>
       </c>
       <c r="T86">
-        <v>2.390958132881178</v>
+        <v>2.550355341739924</v>
       </c>
       <c r="U86">
         <v>0.1186</v>
       </c>
       <c r="V86">
-        <v>0.2677194246646502</v>
+        <v>0.2645697843744779</v>
       </c>
       <c r="W86">
-        <v>0.0868484762347725</v>
+        <v>0.08722202357318694</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8923980822155008</v>
+        <v>0.8818992812482596</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1072988415301449</v>
+        <v>0.1080268415301449</v>
       </c>
       <c r="C87">
-        <v>-1549.581837916193</v>
+        <v>-1684.958625845473</v>
       </c>
       <c r="D87">
-        <v>5618.353162083808</v>
+        <v>5571.127374154527</v>
       </c>
       <c r="E87">
-        <v>5506.135</v>
+        <v>5594.286</v>
       </c>
       <c r="F87">
-        <v>7492.835</v>
+        <v>7580.986</v>
       </c>
       <c r="G87">
         <v>324.9</v>
@@ -8427,37 +8427,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M87">
-        <v>888.6502310000001</v>
+        <v>899.1049396000001</v>
       </c>
       <c r="N87">
-        <v>-104.9502310000001</v>
+        <v>-115.4049396000001</v>
       </c>
       <c r="O87">
-        <v>-31.48506930000004</v>
+        <v>-34.62148188000004</v>
       </c>
       <c r="P87">
-        <v>-73.4651617000001</v>
+        <v>-80.78345772000011</v>
       </c>
       <c r="Q87">
-        <v>320.9348382999999</v>
+        <v>313.6165422799999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2210674766195733</v>
+        <v>0.2335865820924</v>
       </c>
       <c r="T87">
-        <v>2.550355341739924</v>
+        <v>2.732523580435632</v>
       </c>
       <c r="U87">
         <v>0.1186</v>
       </c>
       <c r="V87">
-        <v>0.2645697843744779</v>
+        <v>0.2614933915329142</v>
       </c>
       <c r="W87">
-        <v>0.08722202357318694</v>
+        <v>0.08758688376419639</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8818992812482596</v>
+        <v>0.8716446384430473</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1080268415301449</v>
+        <v>0.1087548415301449</v>
       </c>
       <c r="C88">
-        <v>-1684.958625845473</v>
+        <v>-1819.548106752746</v>
       </c>
       <c r="D88">
-        <v>5571.127374154527</v>
+        <v>5524.688893247255</v>
       </c>
       <c r="E88">
-        <v>5594.286</v>
+        <v>5682.437</v>
       </c>
       <c r="F88">
-        <v>7580.986</v>
+        <v>7669.137000000001</v>
       </c>
       <c r="G88">
         <v>324.9</v>
@@ -8509,37 +8509,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M88">
-        <v>899.1049396000001</v>
+        <v>909.5596482000002</v>
       </c>
       <c r="N88">
-        <v>-115.4049396000001</v>
+        <v>-125.8596482000003</v>
       </c>
       <c r="O88">
-        <v>-34.62148188000004</v>
+        <v>-37.75789446000008</v>
       </c>
       <c r="P88">
-        <v>-80.78345772000011</v>
+        <v>-88.10175374000019</v>
       </c>
       <c r="Q88">
-        <v>313.6165422799999</v>
+        <v>306.2982462599998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2335865820924</v>
+        <v>0.2480317037918154</v>
       </c>
       <c r="T88">
-        <v>2.732523580435632</v>
+        <v>2.942717702007605</v>
       </c>
       <c r="U88">
         <v>0.1186</v>
       </c>
       <c r="V88">
-        <v>0.2614933915329142</v>
+        <v>0.2584877203658691</v>
       </c>
       <c r="W88">
-        <v>0.08758688376419639</v>
+        <v>0.08794335636460793</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8716446384430473</v>
+        <v>0.8616257345528973</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1087548415301449</v>
+        <v>0.1094828415301449</v>
       </c>
       <c r="C89">
-        <v>-1819.548106752746</v>
+        <v>-1953.36980582546</v>
       </c>
       <c r="D89">
-        <v>5524.688893247255</v>
+        <v>5479.01819417454</v>
       </c>
       <c r="E89">
-        <v>5682.437</v>
+        <v>5770.588</v>
       </c>
       <c r="F89">
-        <v>7669.137000000001</v>
+        <v>7757.288</v>
       </c>
       <c r="G89">
         <v>324.9</v>
@@ -8591,37 +8591,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M89">
-        <v>909.5596482000002</v>
+        <v>920.0143568000001</v>
       </c>
       <c r="N89">
-        <v>-125.8596482000003</v>
+        <v>-136.3143568000002</v>
       </c>
       <c r="O89">
-        <v>-37.75789446000008</v>
+        <v>-40.89430704000004</v>
       </c>
       <c r="P89">
-        <v>-88.10175374000019</v>
+        <v>-95.42004976000011</v>
       </c>
       <c r="Q89">
-        <v>306.2982462599998</v>
+        <v>298.9799502399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2480317037918154</v>
+        <v>0.2648843457744667</v>
       </c>
       <c r="T89">
-        <v>2.942717702007605</v>
+        <v>3.187944177174905</v>
       </c>
       <c r="U89">
         <v>0.1186</v>
       </c>
       <c r="V89">
-        <v>0.2584877203658691</v>
+        <v>0.2555503599071661</v>
       </c>
       <c r="W89">
-        <v>0.08794335636460793</v>
+        <v>0.0882917273150101</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8616257345528973</v>
+        <v>0.8518345330238871</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1094828415301449</v>
+        <v>0.1102108415301449</v>
       </c>
       <c r="C90">
-        <v>-1953.36980582546</v>
+        <v>-2086.442607912542</v>
       </c>
       <c r="D90">
-        <v>5479.01819417454</v>
+        <v>5434.096392087458</v>
       </c>
       <c r="E90">
-        <v>5770.588</v>
+        <v>5858.739</v>
       </c>
       <c r="F90">
-        <v>7757.288</v>
+        <v>7845.439</v>
       </c>
       <c r="G90">
         <v>324.9</v>
@@ -8673,37 +8673,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M90">
-        <v>920.0143568000001</v>
+        <v>930.4690654000001</v>
       </c>
       <c r="N90">
-        <v>-136.3143568000002</v>
+        <v>-146.7690654000002</v>
       </c>
       <c r="O90">
-        <v>-40.89430704000004</v>
+        <v>-44.03071962000005</v>
       </c>
       <c r="P90">
-        <v>-95.42004976000011</v>
+        <v>-102.7383457800001</v>
       </c>
       <c r="Q90">
-        <v>298.9799502399999</v>
+        <v>291.6616542199998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2648843457744667</v>
+        <v>0.2848011044812364</v>
       </c>
       <c r="T90">
-        <v>3.187944177174905</v>
+        <v>3.477757284190805</v>
       </c>
       <c r="U90">
         <v>0.1186</v>
       </c>
       <c r="V90">
-        <v>0.2555503599071661</v>
+        <v>0.2526790075486586</v>
       </c>
       <c r="W90">
-        <v>0.0882917273150101</v>
+        <v>0.08863226970472909</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8518345330238871</v>
+        <v>0.8422633584955288</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1102108415301449</v>
+        <v>0.1109388415301449</v>
       </c>
       <c r="C91">
-        <v>-2086.442607912542</v>
+        <v>-2218.784783561207</v>
       </c>
       <c r="D91">
-        <v>5434.096392087458</v>
+        <v>5389.905216438793</v>
       </c>
       <c r="E91">
-        <v>5858.739</v>
+        <v>5946.889999999999</v>
       </c>
       <c r="F91">
-        <v>7845.439</v>
+        <v>7933.59</v>
       </c>
       <c r="G91">
         <v>324.9</v>
@@ -8755,37 +8755,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M91">
-        <v>930.4690654000001</v>
+        <v>940.9237740000001</v>
       </c>
       <c r="N91">
-        <v>-146.7690654000002</v>
+        <v>-157.2237740000002</v>
       </c>
       <c r="O91">
-        <v>-44.03071962000005</v>
+        <v>-47.16713220000005</v>
       </c>
       <c r="P91">
-        <v>-102.7383457800001</v>
+        <v>-110.0566418000001</v>
       </c>
       <c r="Q91">
-        <v>291.6616542199998</v>
+        <v>284.3433581999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2848011044812364</v>
+        <v>0.30870121492936</v>
       </c>
       <c r="T91">
-        <v>3.477757284190805</v>
+        <v>3.825533012609886</v>
       </c>
       <c r="U91">
         <v>0.1186</v>
       </c>
       <c r="V91">
-        <v>0.2526790075486586</v>
+        <v>0.2498714630203402</v>
       </c>
       <c r="W91">
-        <v>0.08863226970472909</v>
+        <v>0.08896524448578766</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8422633584955288</v>
+        <v>0.8329048767344673</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1109388415301449</v>
+        <v>0.1116668415301449</v>
       </c>
       <c r="C92">
-        <v>-2218.784783561207</v>
+        <v>-2350.414013793604</v>
       </c>
       <c r="D92">
-        <v>5389.905216438793</v>
+        <v>5346.426986206397</v>
       </c>
       <c r="E92">
-        <v>5946.889999999999</v>
+        <v>6035.041000000001</v>
       </c>
       <c r="F92">
-        <v>7933.59</v>
+        <v>8021.741000000001</v>
       </c>
       <c r="G92">
         <v>324.9</v>
@@ -8837,37 +8837,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M92">
-        <v>940.9237740000001</v>
+        <v>951.3784826000002</v>
       </c>
       <c r="N92">
-        <v>-157.2237740000002</v>
+        <v>-167.6784826000003</v>
       </c>
       <c r="O92">
-        <v>-47.16713220000005</v>
+        <v>-50.30354478000008</v>
       </c>
       <c r="P92">
-        <v>-110.0566418000001</v>
+        <v>-117.3749378200002</v>
       </c>
       <c r="Q92">
-        <v>284.3433581999999</v>
+        <v>277.0250621799998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.30870121492936</v>
+        <v>0.3379124610326223</v>
       </c>
       <c r="T92">
-        <v>3.825533012609886</v>
+        <v>4.250592236233207</v>
       </c>
       <c r="U92">
         <v>0.1186</v>
       </c>
       <c r="V92">
-        <v>0.2498714630203402</v>
+        <v>0.2471256227673694</v>
       </c>
       <c r="W92">
-        <v>0.08896524448578766</v>
+        <v>0.08929090113979</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8329048767344673</v>
+        <v>0.8237520758912313</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1116668415301449</v>
+        <v>0.1123948415301449</v>
       </c>
       <c r="C93">
-        <v>-2350.414013793604</v>
+        <v>-2481.347413693868</v>
       </c>
       <c r="D93">
-        <v>5346.426986206397</v>
+        <v>5303.644586306133</v>
       </c>
       <c r="E93">
-        <v>6035.041000000001</v>
+        <v>6123.192000000001</v>
       </c>
       <c r="F93">
-        <v>8021.741000000001</v>
+        <v>8109.892000000001</v>
       </c>
       <c r="G93">
         <v>324.9</v>
@@ -8919,37 +8919,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M93">
-        <v>951.3784826000002</v>
+        <v>961.8331912000002</v>
       </c>
       <c r="N93">
-        <v>-167.6784826000003</v>
+        <v>-178.1331912000003</v>
       </c>
       <c r="O93">
-        <v>-50.30354478000008</v>
+        <v>-53.43995736000009</v>
       </c>
       <c r="P93">
-        <v>-117.3749378200002</v>
+        <v>-124.6932338400002</v>
       </c>
       <c r="Q93">
-        <v>277.0250621799998</v>
+        <v>269.7067661599998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3379124610326223</v>
+        <v>0.3744265186617002</v>
       </c>
       <c r="T93">
-        <v>4.250592236233207</v>
+        <v>4.78191626576236</v>
       </c>
       <c r="U93">
         <v>0.1186</v>
       </c>
       <c r="V93">
-        <v>0.2471256227673694</v>
+        <v>0.244439474693811</v>
       </c>
       <c r="W93">
-        <v>0.08929090113979</v>
+        <v>0.08960947830131402</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8237520758912313</v>
+        <v>0.8147982489793701</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1123948415301449</v>
+        <v>0.1131228415301449</v>
       </c>
       <c r="C94">
-        <v>-2481.347413693868</v>
+        <v>-2611.601554871717</v>
       </c>
       <c r="D94">
-        <v>5303.644586306133</v>
+        <v>5261.541445128285</v>
       </c>
       <c r="E94">
-        <v>6123.192000000001</v>
+        <v>6211.343000000001</v>
       </c>
       <c r="F94">
-        <v>8109.892000000001</v>
+        <v>8198.043000000001</v>
       </c>
       <c r="G94">
         <v>324.9</v>
@@ -9001,37 +9001,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M94">
-        <v>961.8331912000002</v>
+        <v>972.2878998000002</v>
       </c>
       <c r="N94">
-        <v>-178.1331912000003</v>
+        <v>-188.5878998000003</v>
       </c>
       <c r="O94">
-        <v>-53.43995736000009</v>
+        <v>-56.57636994000008</v>
       </c>
       <c r="P94">
-        <v>-124.6932338400002</v>
+        <v>-132.0115298600002</v>
       </c>
       <c r="Q94">
-        <v>269.7067661599998</v>
+        <v>262.3884701399998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3744265186617002</v>
+        <v>0.4213731641848003</v>
       </c>
       <c r="T94">
-        <v>4.78191626576236</v>
+        <v>5.465047160871269</v>
       </c>
       <c r="U94">
         <v>0.1186</v>
       </c>
       <c r="V94">
-        <v>0.244439474693811</v>
+        <v>0.2418110932454905</v>
       </c>
       <c r="W94">
-        <v>0.08960947830131402</v>
+        <v>0.08992120434108485</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8147982489793701</v>
+        <v>0.8060369774849683</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1131228415301449</v>
+        <v>0.194241276102966</v>
       </c>
       <c r="C95">
-        <v>-2611.601554871717</v>
+        <v>-5169.376562390096</v>
       </c>
       <c r="D95">
-        <v>5261.541445128285</v>
+        <v>2791.917437609904</v>
       </c>
       <c r="E95">
-        <v>6211.343000000001</v>
+        <v>6299.494000000001</v>
       </c>
       <c r="F95">
-        <v>8198.043000000001</v>
+        <v>8286.194000000001</v>
       </c>
       <c r="G95">
         <v>324.9</v>
@@ -9083,45 +9083,45 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M95">
-        <v>972.2878998000002</v>
+        <v>1663.8677552</v>
       </c>
       <c r="N95">
-        <v>-188.5878998000003</v>
+        <v>-880.1677552000004</v>
       </c>
       <c r="O95">
-        <v>-56.57636994000008</v>
+        <v>-264.0503265600001</v>
       </c>
       <c r="P95">
-        <v>-132.0115298600002</v>
+        <v>-616.1174286400003</v>
       </c>
       <c r="Q95">
-        <v>262.3884701399998</v>
+        <v>-221.7174286400003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4213731641848003</v>
+        <v>0.5360092677626183</v>
       </c>
       <c r="T95">
-        <v>5.465047160871269</v>
+        <v>7.133142147772502</v>
       </c>
       <c r="U95">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.2418110932454905</v>
+        <v>0.1413032972513728</v>
       </c>
       <c r="W95">
-        <v>0.08992120434108485</v>
+        <v>0.1724262979119243</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.8060369774849683</v>
+        <v>0.4710109908379092</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.194241276102966</v>
+        <v>0.195791276102966</v>
       </c>
       <c r="C96">
-        <v>-5169.376562390096</v>
+        <v>-5282.344880802411</v>
       </c>
       <c r="D96">
-        <v>2791.917437609904</v>
+        <v>2767.100119197589</v>
       </c>
       <c r="E96">
-        <v>6299.494000000001</v>
+        <v>6387.645</v>
       </c>
       <c r="F96">
-        <v>8286.194000000001</v>
+        <v>8374.345000000001</v>
       </c>
       <c r="G96">
         <v>324.9</v>
@@ -9165,37 +9165,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M96">
-        <v>1663.8677552</v>
+        <v>1681.568476</v>
       </c>
       <c r="N96">
-        <v>-880.1677552000004</v>
+        <v>-897.8684760000004</v>
       </c>
       <c r="O96">
-        <v>-264.0503265600001</v>
+        <v>-269.3605428000001</v>
       </c>
       <c r="P96">
-        <v>-616.1174286400003</v>
+        <v>-628.5079332000003</v>
       </c>
       <c r="Q96">
-        <v>-221.7174286400003</v>
+        <v>-234.1079332000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5360092677626183</v>
+        <v>0.6340511213151422</v>
       </c>
       <c r="T96">
-        <v>7.133142147772502</v>
+        <v>8.559770577327008</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1413032972513728</v>
+        <v>0.1398158941224109</v>
       </c>
       <c r="W96">
-        <v>0.1724262979119243</v>
+        <v>0.1727249684602199</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4710109908379092</v>
+        <v>0.4660529804080364</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.195791276102966</v>
+        <v>0.197341276102966</v>
       </c>
       <c r="C97">
-        <v>-5282.344880802411</v>
+        <v>-5394.875884844347</v>
       </c>
       <c r="D97">
-        <v>2767.100119197589</v>
+        <v>2742.720115155654</v>
       </c>
       <c r="E97">
-        <v>6387.645</v>
+        <v>6475.796</v>
       </c>
       <c r="F97">
-        <v>8374.345000000001</v>
+        <v>8462.496000000001</v>
       </c>
       <c r="G97">
         <v>324.9</v>
@@ -9247,37 +9247,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M97">
-        <v>1681.568476</v>
+        <v>1699.2691968</v>
       </c>
       <c r="N97">
-        <v>-897.8684760000004</v>
+        <v>-915.5691968000002</v>
       </c>
       <c r="O97">
-        <v>-269.3605428000001</v>
+        <v>-274.6707590400001</v>
       </c>
       <c r="P97">
-        <v>-628.5079332000003</v>
+        <v>-640.8984377600002</v>
       </c>
       <c r="Q97">
-        <v>-234.1079332000003</v>
+        <v>-246.4984377600002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6340511213151422</v>
+        <v>0.781113901643928</v>
       </c>
       <c r="T97">
-        <v>8.559770577327008</v>
+        <v>10.69971322165876</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1398158941224109</v>
+        <v>0.1383594785586358</v>
       </c>
       <c r="W97">
-        <v>0.1727249684602199</v>
+        <v>0.1730174167054259</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4660529804080364</v>
+        <v>0.4611982618621195</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.197341276102966</v>
+        <v>0.198891276102966</v>
       </c>
       <c r="C98">
-        <v>-5394.875884844345</v>
+        <v>-5506.981032658873</v>
       </c>
       <c r="D98">
-        <v>2742.720115155655</v>
+        <v>2718.765967341128</v>
       </c>
       <c r="E98">
-        <v>6475.795999999998</v>
+        <v>6563.947</v>
       </c>
       <c r="F98">
-        <v>8462.495999999999</v>
+        <v>8550.647000000001</v>
       </c>
       <c r="G98">
         <v>324.9</v>
@@ -9329,37 +9329,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M98">
-        <v>1699.2691968</v>
+        <v>1716.9699176</v>
       </c>
       <c r="N98">
-        <v>-915.5691968</v>
+        <v>-933.2699176000002</v>
       </c>
       <c r="O98">
-        <v>-274.67075904</v>
+        <v>-279.9809752800001</v>
       </c>
       <c r="P98">
-        <v>-640.89843776</v>
+        <v>-653.2889423200002</v>
       </c>
       <c r="Q98">
-        <v>-246.49843776</v>
+        <v>-258.8889423200002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.781113901643926</v>
+        <v>1.026218535525235</v>
       </c>
       <c r="T98">
-        <v>10.69971322165873</v>
+        <v>14.26628429554498</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1383594785586359</v>
+        <v>0.1369330921817427</v>
       </c>
       <c r="W98">
-        <v>0.1730174167054259</v>
+        <v>0.1733038350899061</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4611982618621195</v>
+        <v>0.456443640605809</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.198891276102966</v>
+        <v>0.2004412761029659</v>
       </c>
       <c r="C99">
-        <v>-5506.981032658873</v>
+        <v>-5618.671385565882</v>
       </c>
       <c r="D99">
-        <v>2718.765967341128</v>
+        <v>2695.226614434119</v>
       </c>
       <c r="E99">
-        <v>6563.947</v>
+        <v>6652.098</v>
       </c>
       <c r="F99">
-        <v>8550.647000000001</v>
+        <v>8638.798000000001</v>
       </c>
       <c r="G99">
         <v>324.9</v>
@@ -9411,37 +9411,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M99">
-        <v>1716.9699176</v>
+        <v>1734.6706384</v>
       </c>
       <c r="N99">
-        <v>-933.2699176000002</v>
+        <v>-950.9706384000002</v>
       </c>
       <c r="O99">
-        <v>-279.9809752800001</v>
+        <v>-285.29119152</v>
       </c>
       <c r="P99">
-        <v>-653.2889423200002</v>
+        <v>-665.6794468800001</v>
       </c>
       <c r="Q99">
-        <v>-258.8889423200002</v>
+        <v>-271.2794468800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.026218535525235</v>
+        <v>1.516427803287852</v>
       </c>
       <c r="T99">
-        <v>14.26628429554498</v>
+        <v>21.39942644331747</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1369330921817427</v>
+        <v>0.1355358157309086</v>
       </c>
       <c r="W99">
-        <v>0.1733038350899061</v>
+        <v>0.1735844082012336</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.456443640605809</v>
+        <v>0.4517860524363619</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2004412761029659</v>
+        <v>0.201991276102966</v>
       </c>
       <c r="C100">
-        <v>-5618.671385565882</v>
+        <v>-5729.957625093399</v>
       </c>
       <c r="D100">
-        <v>2695.226614434119</v>
+        <v>2672.091374906601</v>
       </c>
       <c r="E100">
-        <v>6652.098</v>
+        <v>6740.249</v>
       </c>
       <c r="F100">
-        <v>8638.798000000001</v>
+        <v>8726.949000000001</v>
       </c>
       <c r="G100">
         <v>324.9</v>
@@ -9493,37 +9493,37 @@
         <v>783.6999999999999</v>
       </c>
       <c r="M100">
-        <v>1734.6706384</v>
+        <v>1752.3713592</v>
       </c>
       <c r="N100">
-        <v>-950.9706384000002</v>
+        <v>-968.6713592000002</v>
       </c>
       <c r="O100">
-        <v>-285.29119152</v>
+        <v>-290.60140776</v>
       </c>
       <c r="P100">
-        <v>-665.6794468800001</v>
+        <v>-678.0699514400002</v>
       </c>
       <c r="Q100">
-        <v>-271.2794468800001</v>
+        <v>-283.6699514400002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.516427803287852</v>
+        <v>2.987055606575704</v>
       </c>
       <c r="T100">
-        <v>21.39942644331747</v>
+        <v>42.79885288663494</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1355358157309086</v>
+        <v>0.134166767087162</v>
       </c>
       <c r="W100">
-        <v>0.1735844082012336</v>
+        <v>0.1738593131688979</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4517860524363619</v>
+        <v>0.4472225569572068</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.201991276102966</v>
-      </c>
-      <c r="C101">
-        <v>-5729.957625093399</v>
-      </c>
-      <c r="D101">
-        <v>2672.091374906601</v>
-      </c>
-      <c r="E101">
-        <v>6740.249</v>
-      </c>
-      <c r="F101">
-        <v>8726.949000000001</v>
-      </c>
-      <c r="G101">
-        <v>324.9</v>
-      </c>
-      <c r="H101">
-        <v>6828.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1178.1</v>
-      </c>
-      <c r="K101">
-        <v>394.4</v>
-      </c>
-      <c r="L101">
-        <v>783.6999999999999</v>
-      </c>
-      <c r="M101">
-        <v>1752.3713592</v>
-      </c>
-      <c r="N101">
-        <v>-968.6713592000002</v>
-      </c>
-      <c r="O101">
-        <v>-290.60140776</v>
-      </c>
-      <c r="P101">
-        <v>-678.0699514400002</v>
-      </c>
-      <c r="Q101">
-        <v>-283.6699514400002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.987055606575704</v>
-      </c>
-      <c r="T101">
-        <v>42.79885288663494</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.134166767087162</v>
-      </c>
-      <c r="W101">
-        <v>0.1738593131688979</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4472225569572068</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
